--- a/data/monthly_place/【2025年7月】月次配置.xlsx
+++ b/data/monthly_place/【2025年7月】月次配置.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="97">
   <si>
     <t>レポート開始日</t>
   </si>
@@ -225,6 +225,93 @@
   <si>
     <t>Instagram投稿: 【銀座トレーニングラボ】
 “脚が変わる”は、立ち方から始まる。...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【Dining Bar Lien】...</t>
+  </si>
+  <si>
+    <t>デスクトップ</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【Meibuキッズ空手教室】
+＼ドキドキ💓はじめてのスポーツ体験！／...</t>
+  </si>
+  <si>
+    <t>2026-01-02</t>
+  </si>
+  <si>
+    <t>モバイルウェブ</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【Meibuキッズ空手教室】
+＼2〜3歳のお子さまも大歓迎👶✨／...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 📍町寿司いちもんめ｜福井市大手...</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌸【女性クリニック ラポール】🌸
+すべての世代の女性に、安心と寄り添いを。...</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【髙橋歯科】
+“噛み合わせ”から整える、お口とカラダのトータルケア🪥...</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 📍Wild Crepes - ワイルドクレープス
+安い！旨い！多い！🎉...</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍸【bar moon walk 三条木屋町店】🌙...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍶【駕町 とくさ】熊本・花畑町駅 徒歩5分...</t>
+  </si>
+  <si>
+    <t>炭焼　猿一</t>
+  </si>
+  <si>
+    <t>2026-01-15</t>
+  </si>
+  <si>
+    <t>島田屋　東苗穂店</t>
+  </si>
+  <si>
+    <t>居ZAKKU　CHENOWA</t>
+  </si>
+  <si>
+    <t>三千段の民宿　幸登里</t>
+  </si>
+  <si>
+    <t>てんぐ屋</t>
+  </si>
+  <si>
+    <t>炭火焼肉友丸</t>
+  </si>
+  <si>
+    <t>旬彩屋　笑味</t>
+  </si>
+  <si>
+    <t>有限会社　大嶋_うまか喰い処 祇園 大しま</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【海鮮と肉料理 ほっかい酒房】🍣🍢✨
+すすきの駅から徒歩3分🚶‍♂️...</t>
   </si>
 </sst>
 </file>
@@ -574,7 +661,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB68"/>
+  <dimension ref="A1:AB166"/>
   <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -5292,6 +5379,7138 @@
       </c>
       <c r="AB68">
         <v>40</v>
+      </c>
+    </row>
+    <row r="69" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>28</v>
+      </c>
+      <c r="B69" t="s">
+        <v>29</v>
+      </c>
+      <c r="C69" t="s">
+        <v>70</v>
+      </c>
+      <c r="D69" t="s">
+        <v>31</v>
+      </c>
+      <c r="E69" t="s">
+        <v>32</v>
+      </c>
+      <c r="F69" t="s">
+        <v>71</v>
+      </c>
+      <c r="G69" t="s">
+        <v>54</v>
+      </c>
+      <c r="H69" t="s">
+        <v>35</v>
+      </c>
+      <c r="K69">
+        <v>2</v>
+      </c>
+      <c r="L69">
+        <v>1.5</v>
+      </c>
+      <c r="N69">
+        <v>160</v>
+      </c>
+      <c r="O69" t="s">
+        <v>36</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>72</v>
+      </c>
+      <c r="R69">
+        <v>3</v>
+      </c>
+      <c r="S69">
+        <v>0</v>
+      </c>
+      <c r="X69">
+        <v>0</v>
+      </c>
+      <c r="Y69">
+        <v>0</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>28</v>
+      </c>
+      <c r="B70" t="s">
+        <v>29</v>
+      </c>
+      <c r="C70" t="s">
+        <v>70</v>
+      </c>
+      <c r="D70" t="s">
+        <v>31</v>
+      </c>
+      <c r="E70" t="s">
+        <v>32</v>
+      </c>
+      <c r="F70" t="s">
+        <v>33</v>
+      </c>
+      <c r="G70" t="s">
+        <v>54</v>
+      </c>
+      <c r="H70" t="s">
+        <v>35</v>
+      </c>
+      <c r="I70">
+        <v>57</v>
+      </c>
+      <c r="J70" t="s">
+        <v>40</v>
+      </c>
+      <c r="K70">
+        <v>1445</v>
+      </c>
+      <c r="L70">
+        <v>1.683737</v>
+      </c>
+      <c r="M70">
+        <v>23.22807018</v>
+      </c>
+      <c r="N70">
+        <v>160</v>
+      </c>
+      <c r="O70" t="s">
+        <v>36</v>
+      </c>
+      <c r="P70">
+        <v>1324</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>72</v>
+      </c>
+      <c r="R70">
+        <v>2433</v>
+      </c>
+      <c r="S70">
+        <v>544.18413499999997</v>
+      </c>
+      <c r="T70">
+        <v>57</v>
+      </c>
+      <c r="V70">
+        <v>23.228069999999999</v>
+      </c>
+      <c r="W70">
+        <v>2.342787</v>
+      </c>
+      <c r="X70">
+        <v>88</v>
+      </c>
+      <c r="Y70">
+        <v>3.6169340000000001</v>
+      </c>
+      <c r="Z70">
+        <v>15.045455</v>
+      </c>
+    </row>
+    <row r="71" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>28</v>
+      </c>
+      <c r="B71" t="s">
+        <v>29</v>
+      </c>
+      <c r="C71" t="s">
+        <v>70</v>
+      </c>
+      <c r="D71" t="s">
+        <v>31</v>
+      </c>
+      <c r="E71" t="s">
+        <v>38</v>
+      </c>
+      <c r="F71" t="s">
+        <v>33</v>
+      </c>
+      <c r="G71" t="s">
+        <v>54</v>
+      </c>
+      <c r="H71" t="s">
+        <v>35</v>
+      </c>
+      <c r="I71">
+        <v>12</v>
+      </c>
+      <c r="J71" t="s">
+        <v>40</v>
+      </c>
+      <c r="K71">
+        <v>523</v>
+      </c>
+      <c r="L71">
+        <v>1.48566</v>
+      </c>
+      <c r="M71">
+        <v>22.583333329999999</v>
+      </c>
+      <c r="N71">
+        <v>160</v>
+      </c>
+      <c r="O71" t="s">
+        <v>36</v>
+      </c>
+      <c r="P71">
+        <v>271</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>72</v>
+      </c>
+      <c r="R71">
+        <v>777</v>
+      </c>
+      <c r="S71">
+        <v>348.77734900000002</v>
+      </c>
+      <c r="T71">
+        <v>12</v>
+      </c>
+      <c r="V71">
+        <v>22.583333</v>
+      </c>
+      <c r="W71">
+        <v>1.5444020000000001</v>
+      </c>
+      <c r="X71">
+        <v>17</v>
+      </c>
+      <c r="Y71">
+        <v>2.1879019999999998</v>
+      </c>
+      <c r="Z71">
+        <v>15.941176</v>
+      </c>
+    </row>
+    <row r="72" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>28</v>
+      </c>
+      <c r="B72" t="s">
+        <v>29</v>
+      </c>
+      <c r="C72" t="s">
+        <v>70</v>
+      </c>
+      <c r="D72" t="s">
+        <v>31</v>
+      </c>
+      <c r="E72" t="s">
+        <v>51</v>
+      </c>
+      <c r="F72" t="s">
+        <v>33</v>
+      </c>
+      <c r="G72" t="s">
+        <v>54</v>
+      </c>
+      <c r="H72" t="s">
+        <v>35</v>
+      </c>
+      <c r="K72">
+        <v>54</v>
+      </c>
+      <c r="L72">
+        <v>1.1481479999999999</v>
+      </c>
+      <c r="N72">
+        <v>160</v>
+      </c>
+      <c r="O72" t="s">
+        <v>36</v>
+      </c>
+      <c r="P72">
+        <v>9</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>72</v>
+      </c>
+      <c r="R72">
+        <v>62</v>
+      </c>
+      <c r="S72">
+        <v>145.16129000000001</v>
+      </c>
+      <c r="X72">
+        <v>0</v>
+      </c>
+      <c r="Y72">
+        <v>0</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>28</v>
+      </c>
+      <c r="B73" t="s">
+        <v>29</v>
+      </c>
+      <c r="C73" t="s">
+        <v>70</v>
+      </c>
+      <c r="D73" t="s">
+        <v>31</v>
+      </c>
+      <c r="E73" t="s">
+        <v>39</v>
+      </c>
+      <c r="F73" t="s">
+        <v>33</v>
+      </c>
+      <c r="G73" t="s">
+        <v>54</v>
+      </c>
+      <c r="H73" t="s">
+        <v>35</v>
+      </c>
+      <c r="I73">
+        <v>16</v>
+      </c>
+      <c r="J73" t="s">
+        <v>40</v>
+      </c>
+      <c r="K73">
+        <v>585</v>
+      </c>
+      <c r="L73">
+        <v>1.3846149999999999</v>
+      </c>
+      <c r="M73">
+        <v>24.375</v>
+      </c>
+      <c r="N73">
+        <v>160</v>
+      </c>
+      <c r="O73" t="s">
+        <v>36</v>
+      </c>
+      <c r="P73">
+        <v>390</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>72</v>
+      </c>
+      <c r="R73">
+        <v>810</v>
+      </c>
+      <c r="S73">
+        <v>481.48148099999997</v>
+      </c>
+      <c r="T73">
+        <v>16</v>
+      </c>
+      <c r="V73">
+        <v>24.375</v>
+      </c>
+      <c r="W73">
+        <v>1.975309</v>
+      </c>
+      <c r="X73">
+        <v>31</v>
+      </c>
+      <c r="Y73">
+        <v>3.8271600000000001</v>
+      </c>
+      <c r="Z73">
+        <v>12.580645000000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>28</v>
+      </c>
+      <c r="B74" t="s">
+        <v>29</v>
+      </c>
+      <c r="C74" t="s">
+        <v>70</v>
+      </c>
+      <c r="D74" t="s">
+        <v>31</v>
+      </c>
+      <c r="E74" t="s">
+        <v>41</v>
+      </c>
+      <c r="F74" t="s">
+        <v>33</v>
+      </c>
+      <c r="G74" t="s">
+        <v>54</v>
+      </c>
+      <c r="H74" t="s">
+        <v>35</v>
+      </c>
+      <c r="I74">
+        <v>114</v>
+      </c>
+      <c r="J74" t="s">
+        <v>40</v>
+      </c>
+      <c r="K74">
+        <v>2555</v>
+      </c>
+      <c r="L74">
+        <v>1.7424660000000001</v>
+      </c>
+      <c r="M74">
+        <v>24.69298246</v>
+      </c>
+      <c r="N74">
+        <v>160</v>
+      </c>
+      <c r="O74" t="s">
+        <v>36</v>
+      </c>
+      <c r="P74">
+        <v>2815</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>72</v>
+      </c>
+      <c r="R74">
+        <v>4452</v>
+      </c>
+      <c r="S74">
+        <v>632.30008999999995</v>
+      </c>
+      <c r="T74">
+        <v>114</v>
+      </c>
+      <c r="V74">
+        <v>24.692982000000001</v>
+      </c>
+      <c r="W74">
+        <v>2.5606469999999999</v>
+      </c>
+      <c r="X74">
+        <v>174</v>
+      </c>
+      <c r="Y74">
+        <v>3.9083559999999999</v>
+      </c>
+      <c r="Z74">
+        <v>16.178160999999999</v>
+      </c>
+    </row>
+    <row r="75" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>28</v>
+      </c>
+      <c r="B75" t="s">
+        <v>29</v>
+      </c>
+      <c r="C75" t="s">
+        <v>73</v>
+      </c>
+      <c r="D75" t="s">
+        <v>31</v>
+      </c>
+      <c r="E75" t="s">
+        <v>32</v>
+      </c>
+      <c r="F75" t="s">
+        <v>71</v>
+      </c>
+      <c r="G75" t="s">
+        <v>34</v>
+      </c>
+      <c r="H75" t="s">
+        <v>35</v>
+      </c>
+      <c r="K75">
+        <v>1</v>
+      </c>
+      <c r="L75">
+        <v>2</v>
+      </c>
+      <c r="N75">
+        <v>160</v>
+      </c>
+      <c r="O75" t="s">
+        <v>36</v>
+      </c>
+      <c r="P75">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>74</v>
+      </c>
+      <c r="R75">
+        <v>2</v>
+      </c>
+      <c r="S75">
+        <v>500</v>
+      </c>
+      <c r="X75">
+        <v>0</v>
+      </c>
+      <c r="Y75">
+        <v>0</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>28</v>
+      </c>
+      <c r="B76" t="s">
+        <v>29</v>
+      </c>
+      <c r="C76" t="s">
+        <v>73</v>
+      </c>
+      <c r="D76" t="s">
+        <v>31</v>
+      </c>
+      <c r="E76" t="s">
+        <v>32</v>
+      </c>
+      <c r="F76" t="s">
+        <v>33</v>
+      </c>
+      <c r="G76" t="s">
+        <v>34</v>
+      </c>
+      <c r="H76" t="s">
+        <v>35</v>
+      </c>
+      <c r="I76">
+        <v>20</v>
+      </c>
+      <c r="J76" t="s">
+        <v>40</v>
+      </c>
+      <c r="K76">
+        <v>680</v>
+      </c>
+      <c r="L76">
+        <v>1.420588</v>
+      </c>
+      <c r="M76">
+        <v>48.35</v>
+      </c>
+      <c r="N76">
+        <v>160</v>
+      </c>
+      <c r="O76" t="s">
+        <v>36</v>
+      </c>
+      <c r="P76">
+        <v>967</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>74</v>
+      </c>
+      <c r="R76">
+        <v>966</v>
+      </c>
+      <c r="S76">
+        <v>1001.035197</v>
+      </c>
+      <c r="T76">
+        <v>20</v>
+      </c>
+      <c r="V76">
+        <v>48.35</v>
+      </c>
+      <c r="W76">
+        <v>2.0703930000000001</v>
+      </c>
+      <c r="X76">
+        <v>29</v>
+      </c>
+      <c r="Y76">
+        <v>3.0020699999999998</v>
+      </c>
+      <c r="Z76">
+        <v>33.344828</v>
+      </c>
+    </row>
+    <row r="77" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>28</v>
+      </c>
+      <c r="B77" t="s">
+        <v>29</v>
+      </c>
+      <c r="C77" t="s">
+        <v>73</v>
+      </c>
+      <c r="D77" t="s">
+        <v>31</v>
+      </c>
+      <c r="E77" t="s">
+        <v>32</v>
+      </c>
+      <c r="F77" t="s">
+        <v>75</v>
+      </c>
+      <c r="G77" t="s">
+        <v>34</v>
+      </c>
+      <c r="H77" t="s">
+        <v>35</v>
+      </c>
+      <c r="I77">
+        <v>1</v>
+      </c>
+      <c r="J77" t="s">
+        <v>40</v>
+      </c>
+      <c r="K77">
+        <v>3</v>
+      </c>
+      <c r="L77">
+        <v>2</v>
+      </c>
+      <c r="M77">
+        <v>12</v>
+      </c>
+      <c r="N77">
+        <v>160</v>
+      </c>
+      <c r="O77" t="s">
+        <v>36</v>
+      </c>
+      <c r="P77">
+        <v>12</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>74</v>
+      </c>
+      <c r="R77">
+        <v>6</v>
+      </c>
+      <c r="S77">
+        <v>2000</v>
+      </c>
+      <c r="T77">
+        <v>1</v>
+      </c>
+      <c r="V77">
+        <v>12</v>
+      </c>
+      <c r="W77">
+        <v>16.666667</v>
+      </c>
+      <c r="X77">
+        <v>1</v>
+      </c>
+      <c r="Y77">
+        <v>16.666667</v>
+      </c>
+      <c r="Z77">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="78" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>28</v>
+      </c>
+      <c r="B78" t="s">
+        <v>29</v>
+      </c>
+      <c r="C78" t="s">
+        <v>73</v>
+      </c>
+      <c r="D78" t="s">
+        <v>31</v>
+      </c>
+      <c r="E78" t="s">
+        <v>38</v>
+      </c>
+      <c r="F78" t="s">
+        <v>33</v>
+      </c>
+      <c r="G78" t="s">
+        <v>34</v>
+      </c>
+      <c r="H78" t="s">
+        <v>35</v>
+      </c>
+      <c r="I78">
+        <v>1</v>
+      </c>
+      <c r="J78" t="s">
+        <v>40</v>
+      </c>
+      <c r="K78">
+        <v>71</v>
+      </c>
+      <c r="L78">
+        <v>1.1971830000000001</v>
+      </c>
+      <c r="M78">
+        <v>75</v>
+      </c>
+      <c r="N78">
+        <v>160</v>
+      </c>
+      <c r="O78" t="s">
+        <v>36</v>
+      </c>
+      <c r="P78">
+        <v>75</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>74</v>
+      </c>
+      <c r="R78">
+        <v>85</v>
+      </c>
+      <c r="S78">
+        <v>882.35294099999999</v>
+      </c>
+      <c r="T78">
+        <v>1</v>
+      </c>
+      <c r="V78">
+        <v>75</v>
+      </c>
+      <c r="W78">
+        <v>1.176471</v>
+      </c>
+      <c r="X78">
+        <v>1</v>
+      </c>
+      <c r="Y78">
+        <v>1.176471</v>
+      </c>
+      <c r="Z78">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="79" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>28</v>
+      </c>
+      <c r="B79" t="s">
+        <v>29</v>
+      </c>
+      <c r="C79" t="s">
+        <v>73</v>
+      </c>
+      <c r="D79" t="s">
+        <v>31</v>
+      </c>
+      <c r="E79" t="s">
+        <v>39</v>
+      </c>
+      <c r="F79" t="s">
+        <v>33</v>
+      </c>
+      <c r="G79" t="s">
+        <v>34</v>
+      </c>
+      <c r="H79" t="s">
+        <v>35</v>
+      </c>
+      <c r="I79">
+        <v>1</v>
+      </c>
+      <c r="J79" t="s">
+        <v>40</v>
+      </c>
+      <c r="K79">
+        <v>201</v>
+      </c>
+      <c r="L79">
+        <v>1.1641790000000001</v>
+      </c>
+      <c r="M79">
+        <v>188</v>
+      </c>
+      <c r="N79">
+        <v>160</v>
+      </c>
+      <c r="O79" t="s">
+        <v>36</v>
+      </c>
+      <c r="P79">
+        <v>188</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>74</v>
+      </c>
+      <c r="R79">
+        <v>234</v>
+      </c>
+      <c r="S79">
+        <v>803.41880300000003</v>
+      </c>
+      <c r="T79">
+        <v>1</v>
+      </c>
+      <c r="V79">
+        <v>188</v>
+      </c>
+      <c r="W79">
+        <v>0.42735000000000001</v>
+      </c>
+      <c r="X79">
+        <v>2</v>
+      </c>
+      <c r="Y79">
+        <v>0.85470100000000004</v>
+      </c>
+      <c r="Z79">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="80" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>28</v>
+      </c>
+      <c r="B80" t="s">
+        <v>29</v>
+      </c>
+      <c r="C80" t="s">
+        <v>73</v>
+      </c>
+      <c r="D80" t="s">
+        <v>31</v>
+      </c>
+      <c r="E80" t="s">
+        <v>41</v>
+      </c>
+      <c r="F80" t="s">
+        <v>33</v>
+      </c>
+      <c r="G80" t="s">
+        <v>34</v>
+      </c>
+      <c r="H80" t="s">
+        <v>35</v>
+      </c>
+      <c r="I80">
+        <v>62</v>
+      </c>
+      <c r="J80" t="s">
+        <v>40</v>
+      </c>
+      <c r="K80">
+        <v>2749</v>
+      </c>
+      <c r="L80">
+        <v>1.229174</v>
+      </c>
+      <c r="M80">
+        <v>50.209677419999998</v>
+      </c>
+      <c r="N80">
+        <v>160</v>
+      </c>
+      <c r="O80" t="s">
+        <v>36</v>
+      </c>
+      <c r="P80">
+        <v>3113</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>74</v>
+      </c>
+      <c r="R80">
+        <v>3379</v>
+      </c>
+      <c r="S80">
+        <v>921.27848500000005</v>
+      </c>
+      <c r="T80">
+        <v>62</v>
+      </c>
+      <c r="V80">
+        <v>50.209676999999999</v>
+      </c>
+      <c r="W80">
+        <v>1.834862</v>
+      </c>
+      <c r="X80">
+        <v>69</v>
+      </c>
+      <c r="Y80">
+        <v>2.0420240000000001</v>
+      </c>
+      <c r="Z80">
+        <v>45.115941999999997</v>
+      </c>
+    </row>
+    <row r="81" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>28</v>
+      </c>
+      <c r="B81" t="s">
+        <v>29</v>
+      </c>
+      <c r="C81" t="s">
+        <v>76</v>
+      </c>
+      <c r="D81" t="s">
+        <v>31</v>
+      </c>
+      <c r="E81" t="s">
+        <v>32</v>
+      </c>
+      <c r="F81" t="s">
+        <v>71</v>
+      </c>
+      <c r="G81" t="s">
+        <v>34</v>
+      </c>
+      <c r="H81" t="s">
+        <v>35</v>
+      </c>
+      <c r="K81">
+        <v>2</v>
+      </c>
+      <c r="L81">
+        <v>1.5</v>
+      </c>
+      <c r="N81">
+        <v>160</v>
+      </c>
+      <c r="O81" t="s">
+        <v>36</v>
+      </c>
+      <c r="P81">
+        <v>2</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>74</v>
+      </c>
+      <c r="R81">
+        <v>3</v>
+      </c>
+      <c r="S81">
+        <v>666.66666699999996</v>
+      </c>
+      <c r="X81">
+        <v>0</v>
+      </c>
+      <c r="Y81">
+        <v>0</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>28</v>
+      </c>
+      <c r="B82" t="s">
+        <v>29</v>
+      </c>
+      <c r="C82" t="s">
+        <v>76</v>
+      </c>
+      <c r="D82" t="s">
+        <v>31</v>
+      </c>
+      <c r="E82" t="s">
+        <v>32</v>
+      </c>
+      <c r="F82" t="s">
+        <v>33</v>
+      </c>
+      <c r="G82" t="s">
+        <v>34</v>
+      </c>
+      <c r="H82" t="s">
+        <v>35</v>
+      </c>
+      <c r="I82">
+        <v>40</v>
+      </c>
+      <c r="J82" t="s">
+        <v>40</v>
+      </c>
+      <c r="K82">
+        <v>1191</v>
+      </c>
+      <c r="L82">
+        <v>1.3224180000000001</v>
+      </c>
+      <c r="M82">
+        <v>26.125</v>
+      </c>
+      <c r="N82">
+        <v>160</v>
+      </c>
+      <c r="O82" t="s">
+        <v>36</v>
+      </c>
+      <c r="P82">
+        <v>1045</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>74</v>
+      </c>
+      <c r="R82">
+        <v>1575</v>
+      </c>
+      <c r="S82">
+        <v>663.49206300000003</v>
+      </c>
+      <c r="T82">
+        <v>40</v>
+      </c>
+      <c r="V82">
+        <v>26.125</v>
+      </c>
+      <c r="W82">
+        <v>2.5396830000000001</v>
+      </c>
+      <c r="X82">
+        <v>52</v>
+      </c>
+      <c r="Y82">
+        <v>3.301587</v>
+      </c>
+      <c r="Z82">
+        <v>20.096153999999999</v>
+      </c>
+    </row>
+    <row r="83" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>28</v>
+      </c>
+      <c r="B83" t="s">
+        <v>29</v>
+      </c>
+      <c r="C83" t="s">
+        <v>76</v>
+      </c>
+      <c r="D83" t="s">
+        <v>31</v>
+      </c>
+      <c r="E83" t="s">
+        <v>32</v>
+      </c>
+      <c r="F83" t="s">
+        <v>75</v>
+      </c>
+      <c r="G83" t="s">
+        <v>34</v>
+      </c>
+      <c r="H83" t="s">
+        <v>35</v>
+      </c>
+      <c r="I83">
+        <v>1</v>
+      </c>
+      <c r="J83" t="s">
+        <v>40</v>
+      </c>
+      <c r="K83">
+        <v>1</v>
+      </c>
+      <c r="L83">
+        <v>2</v>
+      </c>
+      <c r="M83">
+        <v>6</v>
+      </c>
+      <c r="N83">
+        <v>160</v>
+      </c>
+      <c r="O83" t="s">
+        <v>36</v>
+      </c>
+      <c r="P83">
+        <v>6</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>74</v>
+      </c>
+      <c r="R83">
+        <v>2</v>
+      </c>
+      <c r="S83">
+        <v>3000</v>
+      </c>
+      <c r="T83">
+        <v>1</v>
+      </c>
+      <c r="V83">
+        <v>6</v>
+      </c>
+      <c r="W83">
+        <v>50</v>
+      </c>
+      <c r="X83">
+        <v>1</v>
+      </c>
+      <c r="Y83">
+        <v>50</v>
+      </c>
+      <c r="Z83">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>28</v>
+      </c>
+      <c r="B84" t="s">
+        <v>29</v>
+      </c>
+      <c r="C84" t="s">
+        <v>76</v>
+      </c>
+      <c r="D84" t="s">
+        <v>31</v>
+      </c>
+      <c r="E84" t="s">
+        <v>38</v>
+      </c>
+      <c r="F84" t="s">
+        <v>33</v>
+      </c>
+      <c r="G84" t="s">
+        <v>34</v>
+      </c>
+      <c r="H84" t="s">
+        <v>35</v>
+      </c>
+      <c r="I84">
+        <v>2</v>
+      </c>
+      <c r="J84" t="s">
+        <v>40</v>
+      </c>
+      <c r="K84">
+        <v>306</v>
+      </c>
+      <c r="L84">
+        <v>1.1797390000000001</v>
+      </c>
+      <c r="M84">
+        <v>73</v>
+      </c>
+      <c r="N84">
+        <v>160</v>
+      </c>
+      <c r="O84" t="s">
+        <v>36</v>
+      </c>
+      <c r="P84">
+        <v>146</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>74</v>
+      </c>
+      <c r="R84">
+        <v>361</v>
+      </c>
+      <c r="S84">
+        <v>404.43213300000002</v>
+      </c>
+      <c r="T84">
+        <v>2</v>
+      </c>
+      <c r="V84">
+        <v>73</v>
+      </c>
+      <c r="W84">
+        <v>0.55401699999999998</v>
+      </c>
+      <c r="X84">
+        <v>6</v>
+      </c>
+      <c r="Y84">
+        <v>1.66205</v>
+      </c>
+      <c r="Z84">
+        <v>24.333333</v>
+      </c>
+    </row>
+    <row r="85" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>28</v>
+      </c>
+      <c r="B85" t="s">
+        <v>29</v>
+      </c>
+      <c r="C85" t="s">
+        <v>76</v>
+      </c>
+      <c r="D85" t="s">
+        <v>31</v>
+      </c>
+      <c r="E85" t="s">
+        <v>51</v>
+      </c>
+      <c r="F85" t="s">
+        <v>33</v>
+      </c>
+      <c r="G85" t="s">
+        <v>34</v>
+      </c>
+      <c r="H85" t="s">
+        <v>35</v>
+      </c>
+      <c r="I85">
+        <v>1</v>
+      </c>
+      <c r="J85" t="s">
+        <v>40</v>
+      </c>
+      <c r="K85">
+        <v>71</v>
+      </c>
+      <c r="L85">
+        <v>1.1971830000000001</v>
+      </c>
+      <c r="M85">
+        <v>18</v>
+      </c>
+      <c r="N85">
+        <v>160</v>
+      </c>
+      <c r="O85" t="s">
+        <v>36</v>
+      </c>
+      <c r="P85">
+        <v>18</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>74</v>
+      </c>
+      <c r="R85">
+        <v>85</v>
+      </c>
+      <c r="S85">
+        <v>211.76470599999999</v>
+      </c>
+      <c r="T85">
+        <v>1</v>
+      </c>
+      <c r="V85">
+        <v>18</v>
+      </c>
+      <c r="W85">
+        <v>1.176471</v>
+      </c>
+      <c r="X85">
+        <v>2</v>
+      </c>
+      <c r="Y85">
+        <v>2.3529409999999999</v>
+      </c>
+      <c r="Z85">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>28</v>
+      </c>
+      <c r="B86" t="s">
+        <v>29</v>
+      </c>
+      <c r="C86" t="s">
+        <v>76</v>
+      </c>
+      <c r="D86" t="s">
+        <v>31</v>
+      </c>
+      <c r="E86" t="s">
+        <v>39</v>
+      </c>
+      <c r="F86" t="s">
+        <v>33</v>
+      </c>
+      <c r="G86" t="s">
+        <v>34</v>
+      </c>
+      <c r="H86" t="s">
+        <v>35</v>
+      </c>
+      <c r="I86">
+        <v>6</v>
+      </c>
+      <c r="J86" t="s">
+        <v>40</v>
+      </c>
+      <c r="K86">
+        <v>240</v>
+      </c>
+      <c r="L86">
+        <v>1.175</v>
+      </c>
+      <c r="M86">
+        <v>24.5</v>
+      </c>
+      <c r="N86">
+        <v>160</v>
+      </c>
+      <c r="O86" t="s">
+        <v>36</v>
+      </c>
+      <c r="P86">
+        <v>147</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>74</v>
+      </c>
+      <c r="R86">
+        <v>282</v>
+      </c>
+      <c r="S86">
+        <v>521.27659600000004</v>
+      </c>
+      <c r="T86">
+        <v>6</v>
+      </c>
+      <c r="V86">
+        <v>24.5</v>
+      </c>
+      <c r="W86">
+        <v>2.1276600000000001</v>
+      </c>
+      <c r="X86">
+        <v>7</v>
+      </c>
+      <c r="Y86">
+        <v>2.4822700000000002</v>
+      </c>
+      <c r="Z86">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="87" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>28</v>
+      </c>
+      <c r="B87" t="s">
+        <v>29</v>
+      </c>
+      <c r="C87" t="s">
+        <v>76</v>
+      </c>
+      <c r="D87" t="s">
+        <v>31</v>
+      </c>
+      <c r="E87" t="s">
+        <v>41</v>
+      </c>
+      <c r="F87" t="s">
+        <v>33</v>
+      </c>
+      <c r="G87" t="s">
+        <v>34</v>
+      </c>
+      <c r="H87" t="s">
+        <v>35</v>
+      </c>
+      <c r="I87">
+        <v>167</v>
+      </c>
+      <c r="J87" t="s">
+        <v>40</v>
+      </c>
+      <c r="K87">
+        <v>2825</v>
+      </c>
+      <c r="L87">
+        <v>1.2856639999999999</v>
+      </c>
+      <c r="M87">
+        <v>17.80239521</v>
+      </c>
+      <c r="N87">
+        <v>160</v>
+      </c>
+      <c r="O87" t="s">
+        <v>36</v>
+      </c>
+      <c r="P87">
+        <v>2973</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>74</v>
+      </c>
+      <c r="R87">
+        <v>3632</v>
+      </c>
+      <c r="S87">
+        <v>818.55726900000002</v>
+      </c>
+      <c r="T87">
+        <v>167</v>
+      </c>
+      <c r="V87">
+        <v>17.802395000000001</v>
+      </c>
+      <c r="W87">
+        <v>4.5980179999999997</v>
+      </c>
+      <c r="X87">
+        <v>254</v>
+      </c>
+      <c r="Y87">
+        <v>6.9933920000000001</v>
+      </c>
+      <c r="Z87">
+        <v>11.704724000000001</v>
+      </c>
+    </row>
+    <row r="88" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>28</v>
+      </c>
+      <c r="B88" t="s">
+        <v>29</v>
+      </c>
+      <c r="C88" t="s">
+        <v>77</v>
+      </c>
+      <c r="D88" t="s">
+        <v>31</v>
+      </c>
+      <c r="E88" t="s">
+        <v>32</v>
+      </c>
+      <c r="F88" t="s">
+        <v>71</v>
+      </c>
+      <c r="G88" t="s">
+        <v>34</v>
+      </c>
+      <c r="H88" t="s">
+        <v>35</v>
+      </c>
+      <c r="K88">
+        <v>4</v>
+      </c>
+      <c r="L88">
+        <v>1.5</v>
+      </c>
+      <c r="N88">
+        <v>160</v>
+      </c>
+      <c r="O88" t="s">
+        <v>36</v>
+      </c>
+      <c r="P88">
+        <v>1</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>78</v>
+      </c>
+      <c r="R88">
+        <v>6</v>
+      </c>
+      <c r="S88">
+        <v>166.66666699999999</v>
+      </c>
+      <c r="X88">
+        <v>0</v>
+      </c>
+      <c r="Y88">
+        <v>0</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>28</v>
+      </c>
+      <c r="B89" t="s">
+        <v>29</v>
+      </c>
+      <c r="C89" t="s">
+        <v>77</v>
+      </c>
+      <c r="D89" t="s">
+        <v>31</v>
+      </c>
+      <c r="E89" t="s">
+        <v>32</v>
+      </c>
+      <c r="F89" t="s">
+        <v>33</v>
+      </c>
+      <c r="G89" t="s">
+        <v>34</v>
+      </c>
+      <c r="H89" t="s">
+        <v>35</v>
+      </c>
+      <c r="I89">
+        <v>29</v>
+      </c>
+      <c r="J89" t="s">
+        <v>40</v>
+      </c>
+      <c r="K89">
+        <v>737</v>
+      </c>
+      <c r="L89">
+        <v>1.4341930000000001</v>
+      </c>
+      <c r="M89">
+        <v>22.241379309999999</v>
+      </c>
+      <c r="N89">
+        <v>160</v>
+      </c>
+      <c r="O89" t="s">
+        <v>36</v>
+      </c>
+      <c r="P89">
+        <v>645</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>78</v>
+      </c>
+      <c r="R89">
+        <v>1057</v>
+      </c>
+      <c r="S89">
+        <v>610.21759699999996</v>
+      </c>
+      <c r="T89">
+        <v>29</v>
+      </c>
+      <c r="V89">
+        <v>22.241378999999998</v>
+      </c>
+      <c r="W89">
+        <v>2.743614</v>
+      </c>
+      <c r="X89">
+        <v>33</v>
+      </c>
+      <c r="Y89">
+        <v>3.1220439999999998</v>
+      </c>
+      <c r="Z89">
+        <v>19.545455</v>
+      </c>
+    </row>
+    <row r="90" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>28</v>
+      </c>
+      <c r="B90" t="s">
+        <v>29</v>
+      </c>
+      <c r="C90" t="s">
+        <v>77</v>
+      </c>
+      <c r="D90" t="s">
+        <v>31</v>
+      </c>
+      <c r="E90" t="s">
+        <v>38</v>
+      </c>
+      <c r="F90" t="s">
+        <v>33</v>
+      </c>
+      <c r="G90" t="s">
+        <v>34</v>
+      </c>
+      <c r="H90" t="s">
+        <v>35</v>
+      </c>
+      <c r="I90">
+        <v>6</v>
+      </c>
+      <c r="J90" t="s">
+        <v>40</v>
+      </c>
+      <c r="K90">
+        <v>248</v>
+      </c>
+      <c r="L90">
+        <v>1.3467739999999999</v>
+      </c>
+      <c r="M90">
+        <v>20.5</v>
+      </c>
+      <c r="N90">
+        <v>160</v>
+      </c>
+      <c r="O90" t="s">
+        <v>36</v>
+      </c>
+      <c r="P90">
+        <v>123</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>78</v>
+      </c>
+      <c r="R90">
+        <v>334</v>
+      </c>
+      <c r="S90">
+        <v>368.26347299999998</v>
+      </c>
+      <c r="T90">
+        <v>6</v>
+      </c>
+      <c r="V90">
+        <v>20.5</v>
+      </c>
+      <c r="W90">
+        <v>1.7964070000000001</v>
+      </c>
+      <c r="X90">
+        <v>6</v>
+      </c>
+      <c r="Y90">
+        <v>1.7964070000000001</v>
+      </c>
+      <c r="Z90">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>28</v>
+      </c>
+      <c r="B91" t="s">
+        <v>29</v>
+      </c>
+      <c r="C91" t="s">
+        <v>77</v>
+      </c>
+      <c r="D91" t="s">
+        <v>31</v>
+      </c>
+      <c r="E91" t="s">
+        <v>51</v>
+      </c>
+      <c r="F91" t="s">
+        <v>33</v>
+      </c>
+      <c r="G91" t="s">
+        <v>34</v>
+      </c>
+      <c r="H91" t="s">
+        <v>35</v>
+      </c>
+      <c r="K91">
+        <v>18</v>
+      </c>
+      <c r="L91">
+        <v>1.1666669999999999</v>
+      </c>
+      <c r="N91">
+        <v>160</v>
+      </c>
+      <c r="O91" t="s">
+        <v>36</v>
+      </c>
+      <c r="P91">
+        <v>1</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>78</v>
+      </c>
+      <c r="R91">
+        <v>21</v>
+      </c>
+      <c r="S91">
+        <v>47.619047999999999</v>
+      </c>
+      <c r="X91">
+        <v>0</v>
+      </c>
+      <c r="Y91">
+        <v>0</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>28</v>
+      </c>
+      <c r="B92" t="s">
+        <v>29</v>
+      </c>
+      <c r="C92" t="s">
+        <v>77</v>
+      </c>
+      <c r="D92" t="s">
+        <v>31</v>
+      </c>
+      <c r="E92" t="s">
+        <v>39</v>
+      </c>
+      <c r="F92" t="s">
+        <v>33</v>
+      </c>
+      <c r="G92" t="s">
+        <v>34</v>
+      </c>
+      <c r="H92" t="s">
+        <v>35</v>
+      </c>
+      <c r="I92">
+        <v>14</v>
+      </c>
+      <c r="J92" t="s">
+        <v>40</v>
+      </c>
+      <c r="K92">
+        <v>414</v>
+      </c>
+      <c r="L92">
+        <v>1.3188409999999999</v>
+      </c>
+      <c r="M92">
+        <v>25.571428569999998</v>
+      </c>
+      <c r="N92">
+        <v>160</v>
+      </c>
+      <c r="O92" t="s">
+        <v>36</v>
+      </c>
+      <c r="P92">
+        <v>358</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>78</v>
+      </c>
+      <c r="R92">
+        <v>546</v>
+      </c>
+      <c r="S92">
+        <v>655.67765599999996</v>
+      </c>
+      <c r="T92">
+        <v>14</v>
+      </c>
+      <c r="V92">
+        <v>25.571428999999998</v>
+      </c>
+      <c r="W92">
+        <v>2.5641029999999998</v>
+      </c>
+      <c r="X92">
+        <v>17</v>
+      </c>
+      <c r="Y92">
+        <v>3.113553</v>
+      </c>
+      <c r="Z92">
+        <v>21.058824000000001</v>
+      </c>
+    </row>
+    <row r="93" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>28</v>
+      </c>
+      <c r="B93" t="s">
+        <v>29</v>
+      </c>
+      <c r="C93" t="s">
+        <v>77</v>
+      </c>
+      <c r="D93" t="s">
+        <v>31</v>
+      </c>
+      <c r="E93" t="s">
+        <v>41</v>
+      </c>
+      <c r="F93" t="s">
+        <v>33</v>
+      </c>
+      <c r="G93" t="s">
+        <v>34</v>
+      </c>
+      <c r="H93" t="s">
+        <v>35</v>
+      </c>
+      <c r="I93">
+        <v>134</v>
+      </c>
+      <c r="J93" t="s">
+        <v>40</v>
+      </c>
+      <c r="K93">
+        <v>1690</v>
+      </c>
+      <c r="L93">
+        <v>1.494083</v>
+      </c>
+      <c r="M93">
+        <v>20.59701493</v>
+      </c>
+      <c r="N93">
+        <v>160</v>
+      </c>
+      <c r="O93" t="s">
+        <v>36</v>
+      </c>
+      <c r="P93">
+        <v>2760</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>78</v>
+      </c>
+      <c r="R93">
+        <v>2525</v>
+      </c>
+      <c r="S93">
+        <v>1093.069307</v>
+      </c>
+      <c r="T93">
+        <v>134</v>
+      </c>
+      <c r="V93">
+        <v>20.597014999999999</v>
+      </c>
+      <c r="W93">
+        <v>5.3069309999999996</v>
+      </c>
+      <c r="X93">
+        <v>151</v>
+      </c>
+      <c r="Y93">
+        <v>5.9801979999999997</v>
+      </c>
+      <c r="Z93">
+        <v>18.278146</v>
+      </c>
+    </row>
+    <row r="94" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>28</v>
+      </c>
+      <c r="B94" t="s">
+        <v>29</v>
+      </c>
+      <c r="C94" t="s">
+        <v>79</v>
+      </c>
+      <c r="D94" t="s">
+        <v>31</v>
+      </c>
+      <c r="E94" t="s">
+        <v>32</v>
+      </c>
+      <c r="F94" t="s">
+        <v>71</v>
+      </c>
+      <c r="G94" t="s">
+        <v>54</v>
+      </c>
+      <c r="H94" t="s">
+        <v>35</v>
+      </c>
+      <c r="K94">
+        <v>1</v>
+      </c>
+      <c r="L94">
+        <v>1</v>
+      </c>
+      <c r="N94">
+        <v>160</v>
+      </c>
+      <c r="O94" t="s">
+        <v>36</v>
+      </c>
+      <c r="P94">
+        <v>3</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>80</v>
+      </c>
+      <c r="R94">
+        <v>1</v>
+      </c>
+      <c r="S94">
+        <v>3000</v>
+      </c>
+      <c r="X94">
+        <v>0</v>
+      </c>
+      <c r="Y94">
+        <v>0</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>28</v>
+      </c>
+      <c r="B95" t="s">
+        <v>29</v>
+      </c>
+      <c r="C95" t="s">
+        <v>79</v>
+      </c>
+      <c r="D95" t="s">
+        <v>31</v>
+      </c>
+      <c r="E95" t="s">
+        <v>32</v>
+      </c>
+      <c r="F95" t="s">
+        <v>33</v>
+      </c>
+      <c r="G95" t="s">
+        <v>54</v>
+      </c>
+      <c r="H95" t="s">
+        <v>35</v>
+      </c>
+      <c r="I95">
+        <v>48</v>
+      </c>
+      <c r="J95" t="s">
+        <v>40</v>
+      </c>
+      <c r="K95">
+        <v>1198</v>
+      </c>
+      <c r="L95">
+        <v>1.4315530000000001</v>
+      </c>
+      <c r="M95">
+        <v>27.833333329999999</v>
+      </c>
+      <c r="N95">
+        <v>160</v>
+      </c>
+      <c r="O95" t="s">
+        <v>36</v>
+      </c>
+      <c r="P95">
+        <v>1336</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>80</v>
+      </c>
+      <c r="R95">
+        <v>1715</v>
+      </c>
+      <c r="S95">
+        <v>779.00874599999997</v>
+      </c>
+      <c r="T95">
+        <v>48</v>
+      </c>
+      <c r="V95">
+        <v>27.833333</v>
+      </c>
+      <c r="W95">
+        <v>2.7988339999999998</v>
+      </c>
+      <c r="X95">
+        <v>58</v>
+      </c>
+      <c r="Y95">
+        <v>3.3819240000000002</v>
+      </c>
+      <c r="Z95">
+        <v>23.034483000000002</v>
+      </c>
+    </row>
+    <row r="96" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>28</v>
+      </c>
+      <c r="B96" t="s">
+        <v>29</v>
+      </c>
+      <c r="C96" t="s">
+        <v>79</v>
+      </c>
+      <c r="D96" t="s">
+        <v>31</v>
+      </c>
+      <c r="E96" t="s">
+        <v>38</v>
+      </c>
+      <c r="F96" t="s">
+        <v>33</v>
+      </c>
+      <c r="G96" t="s">
+        <v>54</v>
+      </c>
+      <c r="H96" t="s">
+        <v>35</v>
+      </c>
+      <c r="I96">
+        <v>6</v>
+      </c>
+      <c r="J96" t="s">
+        <v>40</v>
+      </c>
+      <c r="K96">
+        <v>269</v>
+      </c>
+      <c r="L96">
+        <v>1.2973980000000001</v>
+      </c>
+      <c r="M96">
+        <v>28</v>
+      </c>
+      <c r="N96">
+        <v>160</v>
+      </c>
+      <c r="O96" t="s">
+        <v>36</v>
+      </c>
+      <c r="P96">
+        <v>168</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>80</v>
+      </c>
+      <c r="R96">
+        <v>349</v>
+      </c>
+      <c r="S96">
+        <v>481.37535800000001</v>
+      </c>
+      <c r="T96">
+        <v>6</v>
+      </c>
+      <c r="V96">
+        <v>28</v>
+      </c>
+      <c r="W96">
+        <v>1.719198</v>
+      </c>
+      <c r="X96">
+        <v>6</v>
+      </c>
+      <c r="Y96">
+        <v>1.719198</v>
+      </c>
+      <c r="Z96">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="97" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>28</v>
+      </c>
+      <c r="B97" t="s">
+        <v>29</v>
+      </c>
+      <c r="C97" t="s">
+        <v>79</v>
+      </c>
+      <c r="D97" t="s">
+        <v>31</v>
+      </c>
+      <c r="E97" t="s">
+        <v>51</v>
+      </c>
+      <c r="F97" t="s">
+        <v>33</v>
+      </c>
+      <c r="G97" t="s">
+        <v>54</v>
+      </c>
+      <c r="H97" t="s">
+        <v>35</v>
+      </c>
+      <c r="K97">
+        <v>42</v>
+      </c>
+      <c r="L97">
+        <v>1.214286</v>
+      </c>
+      <c r="N97">
+        <v>160</v>
+      </c>
+      <c r="O97" t="s">
+        <v>36</v>
+      </c>
+      <c r="P97">
+        <v>7</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>80</v>
+      </c>
+      <c r="R97">
+        <v>51</v>
+      </c>
+      <c r="S97">
+        <v>137.25490199999999</v>
+      </c>
+      <c r="X97">
+        <v>0</v>
+      </c>
+      <c r="Y97">
+        <v>0</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>28</v>
+      </c>
+      <c r="B98" t="s">
+        <v>29</v>
+      </c>
+      <c r="C98" t="s">
+        <v>79</v>
+      </c>
+      <c r="D98" t="s">
+        <v>31</v>
+      </c>
+      <c r="E98" t="s">
+        <v>39</v>
+      </c>
+      <c r="F98" t="s">
+        <v>33</v>
+      </c>
+      <c r="G98" t="s">
+        <v>54</v>
+      </c>
+      <c r="H98" t="s">
+        <v>35</v>
+      </c>
+      <c r="I98">
+        <v>56</v>
+      </c>
+      <c r="J98" t="s">
+        <v>40</v>
+      </c>
+      <c r="K98">
+        <v>1197</v>
+      </c>
+      <c r="L98">
+        <v>1.5146200000000001</v>
+      </c>
+      <c r="M98">
+        <v>29.875</v>
+      </c>
+      <c r="N98">
+        <v>160</v>
+      </c>
+      <c r="O98" t="s">
+        <v>36</v>
+      </c>
+      <c r="P98">
+        <v>1673</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>80</v>
+      </c>
+      <c r="R98">
+        <v>1813</v>
+      </c>
+      <c r="S98">
+        <v>922.77992300000005</v>
+      </c>
+      <c r="T98">
+        <v>56</v>
+      </c>
+      <c r="V98">
+        <v>29.875</v>
+      </c>
+      <c r="W98">
+        <v>3.088803</v>
+      </c>
+      <c r="X98">
+        <v>68</v>
+      </c>
+      <c r="Y98">
+        <v>3.7506889999999999</v>
+      </c>
+      <c r="Z98">
+        <v>24.602941000000001</v>
+      </c>
+    </row>
+    <row r="99" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>28</v>
+      </c>
+      <c r="B99" t="s">
+        <v>29</v>
+      </c>
+      <c r="C99" t="s">
+        <v>79</v>
+      </c>
+      <c r="D99" t="s">
+        <v>31</v>
+      </c>
+      <c r="E99" t="s">
+        <v>41</v>
+      </c>
+      <c r="F99" t="s">
+        <v>33</v>
+      </c>
+      <c r="G99" t="s">
+        <v>54</v>
+      </c>
+      <c r="H99" t="s">
+        <v>35</v>
+      </c>
+      <c r="I99">
+        <v>11</v>
+      </c>
+      <c r="J99" t="s">
+        <v>40</v>
+      </c>
+      <c r="K99">
+        <v>194</v>
+      </c>
+      <c r="L99">
+        <v>1.2577320000000001</v>
+      </c>
+      <c r="M99">
+        <v>34.272727269999997</v>
+      </c>
+      <c r="N99">
+        <v>160</v>
+      </c>
+      <c r="O99" t="s">
+        <v>36</v>
+      </c>
+      <c r="P99">
+        <v>377</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>80</v>
+      </c>
+      <c r="R99">
+        <v>244</v>
+      </c>
+      <c r="S99">
+        <v>1545.0819670000001</v>
+      </c>
+      <c r="T99">
+        <v>11</v>
+      </c>
+      <c r="V99">
+        <v>34.272727000000003</v>
+      </c>
+      <c r="W99">
+        <v>4.508197</v>
+      </c>
+      <c r="X99">
+        <v>14</v>
+      </c>
+      <c r="Y99">
+        <v>5.7377050000000001</v>
+      </c>
+      <c r="Z99">
+        <v>26.928571000000002</v>
+      </c>
+    </row>
+    <row r="100" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>28</v>
+      </c>
+      <c r="B100" t="s">
+        <v>29</v>
+      </c>
+      <c r="C100" t="s">
+        <v>81</v>
+      </c>
+      <c r="D100" t="s">
+        <v>31</v>
+      </c>
+      <c r="E100" t="s">
+        <v>32</v>
+      </c>
+      <c r="F100" t="s">
+        <v>33</v>
+      </c>
+      <c r="G100" t="s">
+        <v>34</v>
+      </c>
+      <c r="H100" t="s">
+        <v>35</v>
+      </c>
+      <c r="I100">
+        <v>12</v>
+      </c>
+      <c r="J100" t="s">
+        <v>40</v>
+      </c>
+      <c r="K100">
+        <v>466</v>
+      </c>
+      <c r="L100">
+        <v>1.347639</v>
+      </c>
+      <c r="M100">
+        <v>43.583333330000002</v>
+      </c>
+      <c r="N100">
+        <v>160</v>
+      </c>
+      <c r="O100" t="s">
+        <v>36</v>
+      </c>
+      <c r="P100">
+        <v>523</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>82</v>
+      </c>
+      <c r="R100">
+        <v>628</v>
+      </c>
+      <c r="S100">
+        <v>832.802548</v>
+      </c>
+      <c r="T100">
+        <v>12</v>
+      </c>
+      <c r="V100">
+        <v>43.583333000000003</v>
+      </c>
+      <c r="W100">
+        <v>1.910828</v>
+      </c>
+      <c r="X100">
+        <v>14</v>
+      </c>
+      <c r="Y100">
+        <v>2.2292990000000001</v>
+      </c>
+      <c r="Z100">
+        <v>37.357143000000001</v>
+      </c>
+    </row>
+    <row r="101" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>28</v>
+      </c>
+      <c r="B101" t="s">
+        <v>29</v>
+      </c>
+      <c r="C101" t="s">
+        <v>81</v>
+      </c>
+      <c r="D101" t="s">
+        <v>31</v>
+      </c>
+      <c r="E101" t="s">
+        <v>38</v>
+      </c>
+      <c r="F101" t="s">
+        <v>33</v>
+      </c>
+      <c r="G101" t="s">
+        <v>34</v>
+      </c>
+      <c r="H101" t="s">
+        <v>35</v>
+      </c>
+      <c r="I101">
+        <v>6</v>
+      </c>
+      <c r="J101" t="s">
+        <v>40</v>
+      </c>
+      <c r="K101">
+        <v>319</v>
+      </c>
+      <c r="L101">
+        <v>1.2946709999999999</v>
+      </c>
+      <c r="M101">
+        <v>33.833333330000002</v>
+      </c>
+      <c r="N101">
+        <v>160</v>
+      </c>
+      <c r="O101" t="s">
+        <v>36</v>
+      </c>
+      <c r="P101">
+        <v>203</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>82</v>
+      </c>
+      <c r="R101">
+        <v>413</v>
+      </c>
+      <c r="S101">
+        <v>491.52542399999999</v>
+      </c>
+      <c r="T101">
+        <v>6</v>
+      </c>
+      <c r="V101">
+        <v>33.833333000000003</v>
+      </c>
+      <c r="W101">
+        <v>1.452785</v>
+      </c>
+      <c r="X101">
+        <v>8</v>
+      </c>
+      <c r="Y101">
+        <v>1.937046</v>
+      </c>
+      <c r="Z101">
+        <v>25.375</v>
+      </c>
+    </row>
+    <row r="102" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>28</v>
+      </c>
+      <c r="B102" t="s">
+        <v>29</v>
+      </c>
+      <c r="C102" t="s">
+        <v>81</v>
+      </c>
+      <c r="D102" t="s">
+        <v>31</v>
+      </c>
+      <c r="E102" t="s">
+        <v>51</v>
+      </c>
+      <c r="F102" t="s">
+        <v>33</v>
+      </c>
+      <c r="G102" t="s">
+        <v>34</v>
+      </c>
+      <c r="H102" t="s">
+        <v>35</v>
+      </c>
+      <c r="K102">
+        <v>59</v>
+      </c>
+      <c r="L102">
+        <v>1.2372879999999999</v>
+      </c>
+      <c r="N102">
+        <v>160</v>
+      </c>
+      <c r="O102" t="s">
+        <v>36</v>
+      </c>
+      <c r="P102">
+        <v>14</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>82</v>
+      </c>
+      <c r="R102">
+        <v>73</v>
+      </c>
+      <c r="S102">
+        <v>191.780822</v>
+      </c>
+      <c r="X102">
+        <v>1</v>
+      </c>
+      <c r="Y102">
+        <v>1.3698630000000001</v>
+      </c>
+      <c r="Z102">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="103" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>28</v>
+      </c>
+      <c r="B103" t="s">
+        <v>29</v>
+      </c>
+      <c r="C103" t="s">
+        <v>81</v>
+      </c>
+      <c r="D103" t="s">
+        <v>31</v>
+      </c>
+      <c r="E103" t="s">
+        <v>39</v>
+      </c>
+      <c r="F103" t="s">
+        <v>33</v>
+      </c>
+      <c r="G103" t="s">
+        <v>34</v>
+      </c>
+      <c r="H103" t="s">
+        <v>35</v>
+      </c>
+      <c r="I103">
+        <v>9</v>
+      </c>
+      <c r="J103" t="s">
+        <v>40</v>
+      </c>
+      <c r="K103">
+        <v>284</v>
+      </c>
+      <c r="L103">
+        <v>1.267606</v>
+      </c>
+      <c r="M103">
+        <v>30.444444440000002</v>
+      </c>
+      <c r="N103">
+        <v>160</v>
+      </c>
+      <c r="O103" t="s">
+        <v>36</v>
+      </c>
+      <c r="P103">
+        <v>274</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>82</v>
+      </c>
+      <c r="R103">
+        <v>360</v>
+      </c>
+      <c r="S103">
+        <v>761.11111100000005</v>
+      </c>
+      <c r="T103">
+        <v>9</v>
+      </c>
+      <c r="V103">
+        <v>30.444444000000001</v>
+      </c>
+      <c r="W103">
+        <v>2.5</v>
+      </c>
+      <c r="X103">
+        <v>13</v>
+      </c>
+      <c r="Y103">
+        <v>3.6111110000000002</v>
+      </c>
+      <c r="Z103">
+        <v>21.076923000000001</v>
+      </c>
+    </row>
+    <row r="104" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>28</v>
+      </c>
+      <c r="B104" t="s">
+        <v>29</v>
+      </c>
+      <c r="C104" t="s">
+        <v>81</v>
+      </c>
+      <c r="D104" t="s">
+        <v>31</v>
+      </c>
+      <c r="E104" t="s">
+        <v>41</v>
+      </c>
+      <c r="F104" t="s">
+        <v>33</v>
+      </c>
+      <c r="G104" t="s">
+        <v>34</v>
+      </c>
+      <c r="H104" t="s">
+        <v>35</v>
+      </c>
+      <c r="I104">
+        <v>75</v>
+      </c>
+      <c r="J104" t="s">
+        <v>40</v>
+      </c>
+      <c r="K104">
+        <v>1488</v>
+      </c>
+      <c r="L104">
+        <v>1.308468</v>
+      </c>
+      <c r="M104">
+        <v>32.253333329999997</v>
+      </c>
+      <c r="N104">
+        <v>160</v>
+      </c>
+      <c r="O104" t="s">
+        <v>36</v>
+      </c>
+      <c r="P104">
+        <v>2419</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>82</v>
+      </c>
+      <c r="R104">
+        <v>1947</v>
+      </c>
+      <c r="S104">
+        <v>1242.424242</v>
+      </c>
+      <c r="T104">
+        <v>75</v>
+      </c>
+      <c r="V104">
+        <v>32.253332999999998</v>
+      </c>
+      <c r="W104">
+        <v>3.8520799999999999</v>
+      </c>
+      <c r="X104">
+        <v>86</v>
+      </c>
+      <c r="Y104">
+        <v>4.417052</v>
+      </c>
+      <c r="Z104">
+        <v>28.127907</v>
+      </c>
+    </row>
+    <row r="105" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>28</v>
+      </c>
+      <c r="B105" t="s">
+        <v>29</v>
+      </c>
+      <c r="C105" t="s">
+        <v>83</v>
+      </c>
+      <c r="D105" t="s">
+        <v>31</v>
+      </c>
+      <c r="E105" t="s">
+        <v>32</v>
+      </c>
+      <c r="F105" t="s">
+        <v>71</v>
+      </c>
+      <c r="G105" t="s">
+        <v>54</v>
+      </c>
+      <c r="H105" t="s">
+        <v>35</v>
+      </c>
+      <c r="K105">
+        <v>5</v>
+      </c>
+      <c r="L105">
+        <v>1.2</v>
+      </c>
+      <c r="N105">
+        <v>160</v>
+      </c>
+      <c r="O105" t="s">
+        <v>36</v>
+      </c>
+      <c r="P105">
+        <v>6</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>84</v>
+      </c>
+      <c r="R105">
+        <v>6</v>
+      </c>
+      <c r="S105">
+        <v>1000</v>
+      </c>
+      <c r="X105">
+        <v>0</v>
+      </c>
+      <c r="Y105">
+        <v>0</v>
+      </c>
+      <c r="Z105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>28</v>
+      </c>
+      <c r="B106" t="s">
+        <v>29</v>
+      </c>
+      <c r="C106" t="s">
+        <v>83</v>
+      </c>
+      <c r="D106" t="s">
+        <v>31</v>
+      </c>
+      <c r="E106" t="s">
+        <v>32</v>
+      </c>
+      <c r="F106" t="s">
+        <v>33</v>
+      </c>
+      <c r="G106" t="s">
+        <v>54</v>
+      </c>
+      <c r="H106" t="s">
+        <v>35</v>
+      </c>
+      <c r="I106">
+        <v>125</v>
+      </c>
+      <c r="J106" t="s">
+        <v>40</v>
+      </c>
+      <c r="K106">
+        <v>2319</v>
+      </c>
+      <c r="L106">
+        <v>1.4980599999999999</v>
+      </c>
+      <c r="M106">
+        <v>12.944000000000001</v>
+      </c>
+      <c r="N106">
+        <v>160</v>
+      </c>
+      <c r="O106" t="s">
+        <v>36</v>
+      </c>
+      <c r="P106">
+        <v>1618</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>84</v>
+      </c>
+      <c r="R106">
+        <v>3474</v>
+      </c>
+      <c r="S106">
+        <v>465.74553800000001</v>
+      </c>
+      <c r="T106">
+        <v>125</v>
+      </c>
+      <c r="V106">
+        <v>12.944000000000001</v>
+      </c>
+      <c r="W106">
+        <v>3.5981580000000002</v>
+      </c>
+      <c r="X106">
+        <v>164</v>
+      </c>
+      <c r="Y106">
+        <v>4.720783</v>
+      </c>
+      <c r="Z106">
+        <v>9.8658540000000006</v>
+      </c>
+    </row>
+    <row r="107" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>28</v>
+      </c>
+      <c r="B107" t="s">
+        <v>29</v>
+      </c>
+      <c r="C107" t="s">
+        <v>83</v>
+      </c>
+      <c r="D107" t="s">
+        <v>31</v>
+      </c>
+      <c r="E107" t="s">
+        <v>32</v>
+      </c>
+      <c r="F107" t="s">
+        <v>75</v>
+      </c>
+      <c r="G107" t="s">
+        <v>54</v>
+      </c>
+      <c r="H107" t="s">
+        <v>35</v>
+      </c>
+      <c r="K107">
+        <v>2</v>
+      </c>
+      <c r="L107">
+        <v>1</v>
+      </c>
+      <c r="N107">
+        <v>160</v>
+      </c>
+      <c r="O107" t="s">
+        <v>36</v>
+      </c>
+      <c r="P107">
+        <v>1</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>84</v>
+      </c>
+      <c r="R107">
+        <v>2</v>
+      </c>
+      <c r="S107">
+        <v>500</v>
+      </c>
+      <c r="X107">
+        <v>0</v>
+      </c>
+      <c r="Y107">
+        <v>0</v>
+      </c>
+      <c r="Z107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>28</v>
+      </c>
+      <c r="B108" t="s">
+        <v>29</v>
+      </c>
+      <c r="C108" t="s">
+        <v>83</v>
+      </c>
+      <c r="D108" t="s">
+        <v>31</v>
+      </c>
+      <c r="E108" t="s">
+        <v>38</v>
+      </c>
+      <c r="F108" t="s">
+        <v>33</v>
+      </c>
+      <c r="G108" t="s">
+        <v>54</v>
+      </c>
+      <c r="H108" t="s">
+        <v>35</v>
+      </c>
+      <c r="I108">
+        <v>22</v>
+      </c>
+      <c r="J108" t="s">
+        <v>40</v>
+      </c>
+      <c r="K108">
+        <v>423</v>
+      </c>
+      <c r="L108">
+        <v>1.326241</v>
+      </c>
+      <c r="M108">
+        <v>9.2272727299999993</v>
+      </c>
+      <c r="N108">
+        <v>160</v>
+      </c>
+      <c r="O108" t="s">
+        <v>36</v>
+      </c>
+      <c r="P108">
+        <v>203</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>84</v>
+      </c>
+      <c r="R108">
+        <v>561</v>
+      </c>
+      <c r="S108">
+        <v>361.85383200000001</v>
+      </c>
+      <c r="T108">
+        <v>22</v>
+      </c>
+      <c r="V108">
+        <v>9.2272730000000003</v>
+      </c>
+      <c r="W108">
+        <v>3.9215689999999999</v>
+      </c>
+      <c r="X108">
+        <v>29</v>
+      </c>
+      <c r="Y108">
+        <v>5.16934</v>
+      </c>
+      <c r="Z108">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="109" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>28</v>
+      </c>
+      <c r="B109" t="s">
+        <v>29</v>
+      </c>
+      <c r="C109" t="s">
+        <v>83</v>
+      </c>
+      <c r="D109" t="s">
+        <v>31</v>
+      </c>
+      <c r="E109" t="s">
+        <v>51</v>
+      </c>
+      <c r="F109" t="s">
+        <v>33</v>
+      </c>
+      <c r="G109" t="s">
+        <v>54</v>
+      </c>
+      <c r="H109" t="s">
+        <v>35</v>
+      </c>
+      <c r="I109">
+        <v>2</v>
+      </c>
+      <c r="J109" t="s">
+        <v>40</v>
+      </c>
+      <c r="K109">
+        <v>27</v>
+      </c>
+      <c r="L109">
+        <v>1.1481479999999999</v>
+      </c>
+      <c r="M109">
+        <v>2</v>
+      </c>
+      <c r="N109">
+        <v>160</v>
+      </c>
+      <c r="O109" t="s">
+        <v>36</v>
+      </c>
+      <c r="P109">
+        <v>4</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>84</v>
+      </c>
+      <c r="R109">
+        <v>31</v>
+      </c>
+      <c r="S109">
+        <v>129.03225800000001</v>
+      </c>
+      <c r="T109">
+        <v>2</v>
+      </c>
+      <c r="V109">
+        <v>2</v>
+      </c>
+      <c r="W109">
+        <v>6.451613</v>
+      </c>
+      <c r="X109">
+        <v>2</v>
+      </c>
+      <c r="Y109">
+        <v>6.451613</v>
+      </c>
+      <c r="Z109">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>28</v>
+      </c>
+      <c r="B110" t="s">
+        <v>29</v>
+      </c>
+      <c r="C110" t="s">
+        <v>83</v>
+      </c>
+      <c r="D110" t="s">
+        <v>31</v>
+      </c>
+      <c r="E110" t="s">
+        <v>39</v>
+      </c>
+      <c r="F110" t="s">
+        <v>33</v>
+      </c>
+      <c r="G110" t="s">
+        <v>54</v>
+      </c>
+      <c r="H110" t="s">
+        <v>35</v>
+      </c>
+      <c r="I110">
+        <v>19</v>
+      </c>
+      <c r="J110" t="s">
+        <v>40</v>
+      </c>
+      <c r="K110">
+        <v>466</v>
+      </c>
+      <c r="L110">
+        <v>1.2188840000000001</v>
+      </c>
+      <c r="M110">
+        <v>15.57894737</v>
+      </c>
+      <c r="N110">
+        <v>160</v>
+      </c>
+      <c r="O110" t="s">
+        <v>36</v>
+      </c>
+      <c r="P110">
+        <v>296</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>84</v>
+      </c>
+      <c r="R110">
+        <v>568</v>
+      </c>
+      <c r="S110">
+        <v>521.12676099999999</v>
+      </c>
+      <c r="T110">
+        <v>19</v>
+      </c>
+      <c r="V110">
+        <v>15.578946999999999</v>
+      </c>
+      <c r="W110">
+        <v>3.3450700000000002</v>
+      </c>
+      <c r="X110">
+        <v>29</v>
+      </c>
+      <c r="Y110">
+        <v>5.1056340000000002</v>
+      </c>
+      <c r="Z110">
+        <v>10.206897</v>
+      </c>
+    </row>
+    <row r="111" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>28</v>
+      </c>
+      <c r="B111" t="s">
+        <v>29</v>
+      </c>
+      <c r="C111" t="s">
+        <v>83</v>
+      </c>
+      <c r="D111" t="s">
+        <v>31</v>
+      </c>
+      <c r="E111" t="s">
+        <v>41</v>
+      </c>
+      <c r="F111" t="s">
+        <v>33</v>
+      </c>
+      <c r="G111" t="s">
+        <v>54</v>
+      </c>
+      <c r="H111" t="s">
+        <v>35</v>
+      </c>
+      <c r="I111">
+        <v>46</v>
+      </c>
+      <c r="J111" t="s">
+        <v>40</v>
+      </c>
+      <c r="K111">
+        <v>722</v>
+      </c>
+      <c r="L111">
+        <v>1.3199449999999999</v>
+      </c>
+      <c r="M111">
+        <v>14.304347829999999</v>
+      </c>
+      <c r="N111">
+        <v>160</v>
+      </c>
+      <c r="O111" t="s">
+        <v>36</v>
+      </c>
+      <c r="P111">
+        <v>658</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>84</v>
+      </c>
+      <c r="R111">
+        <v>953</v>
+      </c>
+      <c r="S111">
+        <v>690.45120699999995</v>
+      </c>
+      <c r="T111">
+        <v>46</v>
+      </c>
+      <c r="V111">
+        <v>14.304347999999999</v>
+      </c>
+      <c r="W111">
+        <v>4.8268630000000003</v>
+      </c>
+      <c r="X111">
+        <v>64</v>
+      </c>
+      <c r="Y111">
+        <v>6.7156349999999998</v>
+      </c>
+      <c r="Z111">
+        <v>10.28125</v>
+      </c>
+    </row>
+    <row r="112" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>28</v>
+      </c>
+      <c r="B112" t="s">
+        <v>29</v>
+      </c>
+      <c r="C112" t="s">
+        <v>85</v>
+      </c>
+      <c r="D112" t="s">
+        <v>31</v>
+      </c>
+      <c r="E112" t="s">
+        <v>32</v>
+      </c>
+      <c r="F112" t="s">
+        <v>33</v>
+      </c>
+      <c r="G112" t="s">
+        <v>54</v>
+      </c>
+      <c r="H112" t="s">
+        <v>35</v>
+      </c>
+      <c r="I112">
+        <v>12</v>
+      </c>
+      <c r="J112" t="s">
+        <v>40</v>
+      </c>
+      <c r="K112">
+        <v>537</v>
+      </c>
+      <c r="L112">
+        <v>1.44879</v>
+      </c>
+      <c r="M112">
+        <v>60.416666669999998</v>
+      </c>
+      <c r="N112">
+        <v>160</v>
+      </c>
+      <c r="O112" t="s">
+        <v>36</v>
+      </c>
+      <c r="P112">
+        <v>725</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>84</v>
+      </c>
+      <c r="R112">
+        <v>778</v>
+      </c>
+      <c r="S112">
+        <v>931.87660700000004</v>
+      </c>
+      <c r="T112">
+        <v>12</v>
+      </c>
+      <c r="V112">
+        <v>60.416666999999997</v>
+      </c>
+      <c r="W112">
+        <v>1.542416</v>
+      </c>
+      <c r="X112">
+        <v>23</v>
+      </c>
+      <c r="Y112">
+        <v>2.9562979999999999</v>
+      </c>
+      <c r="Z112">
+        <v>31.521739</v>
+      </c>
+    </row>
+    <row r="113" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>28</v>
+      </c>
+      <c r="B113" t="s">
+        <v>29</v>
+      </c>
+      <c r="C113" t="s">
+        <v>85</v>
+      </c>
+      <c r="D113" t="s">
+        <v>31</v>
+      </c>
+      <c r="E113" t="s">
+        <v>38</v>
+      </c>
+      <c r="F113" t="s">
+        <v>33</v>
+      </c>
+      <c r="G113" t="s">
+        <v>54</v>
+      </c>
+      <c r="H113" t="s">
+        <v>35</v>
+      </c>
+      <c r="I113">
+        <v>1</v>
+      </c>
+      <c r="J113" t="s">
+        <v>40</v>
+      </c>
+      <c r="K113">
+        <v>169</v>
+      </c>
+      <c r="L113">
+        <v>1.2011829999999999</v>
+      </c>
+      <c r="M113">
+        <v>100</v>
+      </c>
+      <c r="N113">
+        <v>160</v>
+      </c>
+      <c r="O113" t="s">
+        <v>36</v>
+      </c>
+      <c r="P113">
+        <v>100</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>84</v>
+      </c>
+      <c r="R113">
+        <v>203</v>
+      </c>
+      <c r="S113">
+        <v>492.610837</v>
+      </c>
+      <c r="T113">
+        <v>1</v>
+      </c>
+      <c r="V113">
+        <v>100</v>
+      </c>
+      <c r="W113">
+        <v>0.49261100000000002</v>
+      </c>
+      <c r="X113">
+        <v>4</v>
+      </c>
+      <c r="Y113">
+        <v>1.9704429999999999</v>
+      </c>
+      <c r="Z113">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="114" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>28</v>
+      </c>
+      <c r="B114" t="s">
+        <v>29</v>
+      </c>
+      <c r="C114" t="s">
+        <v>85</v>
+      </c>
+      <c r="D114" t="s">
+        <v>31</v>
+      </c>
+      <c r="E114" t="s">
+        <v>51</v>
+      </c>
+      <c r="F114" t="s">
+        <v>33</v>
+      </c>
+      <c r="G114" t="s">
+        <v>54</v>
+      </c>
+      <c r="H114" t="s">
+        <v>35</v>
+      </c>
+      <c r="K114">
+        <v>22</v>
+      </c>
+      <c r="L114">
+        <v>1.1363639999999999</v>
+      </c>
+      <c r="N114">
+        <v>160</v>
+      </c>
+      <c r="O114" t="s">
+        <v>36</v>
+      </c>
+      <c r="P114">
+        <v>1</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>84</v>
+      </c>
+      <c r="R114">
+        <v>25</v>
+      </c>
+      <c r="S114">
+        <v>40</v>
+      </c>
+      <c r="X114">
+        <v>1</v>
+      </c>
+      <c r="Y114">
+        <v>4</v>
+      </c>
+      <c r="Z114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>28</v>
+      </c>
+      <c r="B115" t="s">
+        <v>29</v>
+      </c>
+      <c r="C115" t="s">
+        <v>85</v>
+      </c>
+      <c r="D115" t="s">
+        <v>31</v>
+      </c>
+      <c r="E115" t="s">
+        <v>39</v>
+      </c>
+      <c r="F115" t="s">
+        <v>33</v>
+      </c>
+      <c r="G115" t="s">
+        <v>54</v>
+      </c>
+      <c r="H115" t="s">
+        <v>35</v>
+      </c>
+      <c r="I115">
+        <v>3</v>
+      </c>
+      <c r="J115" t="s">
+        <v>40</v>
+      </c>
+      <c r="K115">
+        <v>97</v>
+      </c>
+      <c r="L115">
+        <v>1.1443300000000001</v>
+      </c>
+      <c r="M115">
+        <v>33</v>
+      </c>
+      <c r="N115">
+        <v>160</v>
+      </c>
+      <c r="O115" t="s">
+        <v>36</v>
+      </c>
+      <c r="P115">
+        <v>99</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>84</v>
+      </c>
+      <c r="R115">
+        <v>111</v>
+      </c>
+      <c r="S115">
+        <v>891.89189199999998</v>
+      </c>
+      <c r="T115">
+        <v>3</v>
+      </c>
+      <c r="V115">
+        <v>33</v>
+      </c>
+      <c r="W115">
+        <v>2.7027030000000001</v>
+      </c>
+      <c r="X115">
+        <v>7</v>
+      </c>
+      <c r="Y115">
+        <v>6.3063060000000002</v>
+      </c>
+      <c r="Z115">
+        <v>14.142856999999999</v>
+      </c>
+    </row>
+    <row r="116" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>28</v>
+      </c>
+      <c r="B116" t="s">
+        <v>29</v>
+      </c>
+      <c r="C116" t="s">
+        <v>85</v>
+      </c>
+      <c r="D116" t="s">
+        <v>31</v>
+      </c>
+      <c r="E116" t="s">
+        <v>41</v>
+      </c>
+      <c r="F116" t="s">
+        <v>33</v>
+      </c>
+      <c r="G116" t="s">
+        <v>54</v>
+      </c>
+      <c r="H116" t="s">
+        <v>35</v>
+      </c>
+      <c r="I116">
+        <v>42</v>
+      </c>
+      <c r="J116" t="s">
+        <v>40</v>
+      </c>
+      <c r="K116">
+        <v>1436</v>
+      </c>
+      <c r="L116">
+        <v>1.479109</v>
+      </c>
+      <c r="M116">
+        <v>44.880952379999997</v>
+      </c>
+      <c r="N116">
+        <v>160</v>
+      </c>
+      <c r="O116" t="s">
+        <v>36</v>
+      </c>
+      <c r="P116">
+        <v>1885</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>84</v>
+      </c>
+      <c r="R116">
+        <v>2124</v>
+      </c>
+      <c r="S116">
+        <v>887.47645999999997</v>
+      </c>
+      <c r="T116">
+        <v>42</v>
+      </c>
+      <c r="V116">
+        <v>44.880952000000001</v>
+      </c>
+      <c r="W116">
+        <v>1.977401</v>
+      </c>
+      <c r="X116">
+        <v>52</v>
+      </c>
+      <c r="Y116">
+        <v>2.4482110000000001</v>
+      </c>
+      <c r="Z116">
+        <v>36.25</v>
+      </c>
+    </row>
+    <row r="117" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>28</v>
+      </c>
+      <c r="B117" t="s">
+        <v>29</v>
+      </c>
+      <c r="C117" t="s">
+        <v>86</v>
+      </c>
+      <c r="D117" t="s">
+        <v>31</v>
+      </c>
+      <c r="E117" t="s">
+        <v>32</v>
+      </c>
+      <c r="F117" t="s">
+        <v>71</v>
+      </c>
+      <c r="G117" t="s">
+        <v>54</v>
+      </c>
+      <c r="H117" t="s">
+        <v>35</v>
+      </c>
+      <c r="I117">
+        <v>1</v>
+      </c>
+      <c r="J117" t="s">
+        <v>40</v>
+      </c>
+      <c r="K117">
+        <v>2</v>
+      </c>
+      <c r="L117">
+        <v>1</v>
+      </c>
+      <c r="M117">
+        <v>2</v>
+      </c>
+      <c r="N117">
+        <v>160</v>
+      </c>
+      <c r="O117" t="s">
+        <v>36</v>
+      </c>
+      <c r="P117">
+        <v>2</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>84</v>
+      </c>
+      <c r="R117">
+        <v>2</v>
+      </c>
+      <c r="S117">
+        <v>1000</v>
+      </c>
+      <c r="T117">
+        <v>1</v>
+      </c>
+      <c r="V117">
+        <v>2</v>
+      </c>
+      <c r="W117">
+        <v>50</v>
+      </c>
+      <c r="X117">
+        <v>2</v>
+      </c>
+      <c r="Y117">
+        <v>100</v>
+      </c>
+      <c r="Z117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>28</v>
+      </c>
+      <c r="B118" t="s">
+        <v>29</v>
+      </c>
+      <c r="C118" t="s">
+        <v>86</v>
+      </c>
+      <c r="D118" t="s">
+        <v>31</v>
+      </c>
+      <c r="E118" t="s">
+        <v>32</v>
+      </c>
+      <c r="F118" t="s">
+        <v>33</v>
+      </c>
+      <c r="G118" t="s">
+        <v>54</v>
+      </c>
+      <c r="H118" t="s">
+        <v>35</v>
+      </c>
+      <c r="I118">
+        <v>52</v>
+      </c>
+      <c r="J118" t="s">
+        <v>40</v>
+      </c>
+      <c r="K118">
+        <v>754</v>
+      </c>
+      <c r="L118">
+        <v>1.5159149999999999</v>
+      </c>
+      <c r="M118">
+        <v>11.44230769</v>
+      </c>
+      <c r="N118">
+        <v>160</v>
+      </c>
+      <c r="O118" t="s">
+        <v>36</v>
+      </c>
+      <c r="P118">
+        <v>595</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>84</v>
+      </c>
+      <c r="R118">
+        <v>1143</v>
+      </c>
+      <c r="S118">
+        <v>520.55993000000001</v>
+      </c>
+      <c r="T118">
+        <v>52</v>
+      </c>
+      <c r="V118">
+        <v>11.442308000000001</v>
+      </c>
+      <c r="W118">
+        <v>4.5494310000000002</v>
+      </c>
+      <c r="X118">
+        <v>53</v>
+      </c>
+      <c r="Y118">
+        <v>4.6369199999999999</v>
+      </c>
+      <c r="Z118">
+        <v>11.226414999999999</v>
+      </c>
+    </row>
+    <row r="119" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>28</v>
+      </c>
+      <c r="B119" t="s">
+        <v>29</v>
+      </c>
+      <c r="C119" t="s">
+        <v>86</v>
+      </c>
+      <c r="D119" t="s">
+        <v>31</v>
+      </c>
+      <c r="E119" t="s">
+        <v>32</v>
+      </c>
+      <c r="F119" t="s">
+        <v>75</v>
+      </c>
+      <c r="G119" t="s">
+        <v>54</v>
+      </c>
+      <c r="H119" t="s">
+        <v>35</v>
+      </c>
+      <c r="K119">
+        <v>1</v>
+      </c>
+      <c r="L119">
+        <v>1</v>
+      </c>
+      <c r="N119">
+        <v>160</v>
+      </c>
+      <c r="O119" t="s">
+        <v>36</v>
+      </c>
+      <c r="P119">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>84</v>
+      </c>
+      <c r="R119">
+        <v>1</v>
+      </c>
+      <c r="S119">
+        <v>0</v>
+      </c>
+      <c r="X119">
+        <v>0</v>
+      </c>
+      <c r="Y119">
+        <v>0</v>
+      </c>
+      <c r="Z119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>28</v>
+      </c>
+      <c r="B120" t="s">
+        <v>29</v>
+      </c>
+      <c r="C120" t="s">
+        <v>86</v>
+      </c>
+      <c r="D120" t="s">
+        <v>31</v>
+      </c>
+      <c r="E120" t="s">
+        <v>38</v>
+      </c>
+      <c r="F120" t="s">
+        <v>33</v>
+      </c>
+      <c r="G120" t="s">
+        <v>54</v>
+      </c>
+      <c r="H120" t="s">
+        <v>35</v>
+      </c>
+      <c r="I120">
+        <v>5</v>
+      </c>
+      <c r="J120" t="s">
+        <v>40</v>
+      </c>
+      <c r="K120">
+        <v>129</v>
+      </c>
+      <c r="L120">
+        <v>1.4263570000000001</v>
+      </c>
+      <c r="M120">
+        <v>13.4</v>
+      </c>
+      <c r="N120">
+        <v>160</v>
+      </c>
+      <c r="O120" t="s">
+        <v>36</v>
+      </c>
+      <c r="P120">
+        <v>67</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>84</v>
+      </c>
+      <c r="R120">
+        <v>184</v>
+      </c>
+      <c r="S120">
+        <v>364.13043499999998</v>
+      </c>
+      <c r="T120">
+        <v>5</v>
+      </c>
+      <c r="V120">
+        <v>13.4</v>
+      </c>
+      <c r="W120">
+        <v>2.7173910000000001</v>
+      </c>
+      <c r="X120">
+        <v>6</v>
+      </c>
+      <c r="Y120">
+        <v>3.2608700000000002</v>
+      </c>
+      <c r="Z120">
+        <v>11.166667</v>
+      </c>
+    </row>
+    <row r="121" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>28</v>
+      </c>
+      <c r="B121" t="s">
+        <v>29</v>
+      </c>
+      <c r="C121" t="s">
+        <v>86</v>
+      </c>
+      <c r="D121" t="s">
+        <v>31</v>
+      </c>
+      <c r="E121" t="s">
+        <v>51</v>
+      </c>
+      <c r="F121" t="s">
+        <v>33</v>
+      </c>
+      <c r="G121" t="s">
+        <v>54</v>
+      </c>
+      <c r="H121" t="s">
+        <v>35</v>
+      </c>
+      <c r="I121">
+        <v>2</v>
+      </c>
+      <c r="J121" t="s">
+        <v>40</v>
+      </c>
+      <c r="K121">
+        <v>37</v>
+      </c>
+      <c r="L121">
+        <v>1.3243240000000001</v>
+      </c>
+      <c r="M121">
+        <v>5.5</v>
+      </c>
+      <c r="N121">
+        <v>160</v>
+      </c>
+      <c r="O121" t="s">
+        <v>36</v>
+      </c>
+      <c r="P121">
+        <v>11</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>84</v>
+      </c>
+      <c r="R121">
+        <v>49</v>
+      </c>
+      <c r="S121">
+        <v>224.48979600000001</v>
+      </c>
+      <c r="T121">
+        <v>2</v>
+      </c>
+      <c r="V121">
+        <v>5.5</v>
+      </c>
+      <c r="W121">
+        <v>4.0816330000000001</v>
+      </c>
+      <c r="X121">
+        <v>2</v>
+      </c>
+      <c r="Y121">
+        <v>4.0816330000000001</v>
+      </c>
+      <c r="Z121">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>28</v>
+      </c>
+      <c r="B122" t="s">
+        <v>29</v>
+      </c>
+      <c r="C122" t="s">
+        <v>86</v>
+      </c>
+      <c r="D122" t="s">
+        <v>31</v>
+      </c>
+      <c r="E122" t="s">
+        <v>39</v>
+      </c>
+      <c r="F122" t="s">
+        <v>33</v>
+      </c>
+      <c r="G122" t="s">
+        <v>54</v>
+      </c>
+      <c r="H122" t="s">
+        <v>35</v>
+      </c>
+      <c r="I122">
+        <v>27</v>
+      </c>
+      <c r="J122" t="s">
+        <v>40</v>
+      </c>
+      <c r="K122">
+        <v>374</v>
+      </c>
+      <c r="L122">
+        <v>1.2994650000000001</v>
+      </c>
+      <c r="M122">
+        <v>13.18518519</v>
+      </c>
+      <c r="N122">
+        <v>160</v>
+      </c>
+      <c r="O122" t="s">
+        <v>36</v>
+      </c>
+      <c r="P122">
+        <v>356</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>84</v>
+      </c>
+      <c r="R122">
+        <v>486</v>
+      </c>
+      <c r="S122">
+        <v>732.51028799999995</v>
+      </c>
+      <c r="T122">
+        <v>27</v>
+      </c>
+      <c r="V122">
+        <v>13.185185000000001</v>
+      </c>
+      <c r="W122">
+        <v>5.5555560000000002</v>
+      </c>
+      <c r="X122">
+        <v>38</v>
+      </c>
+      <c r="Y122">
+        <v>7.8189299999999999</v>
+      </c>
+      <c r="Z122">
+        <v>9.3684209999999997</v>
+      </c>
+    </row>
+    <row r="123" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>28</v>
+      </c>
+      <c r="B123" t="s">
+        <v>29</v>
+      </c>
+      <c r="C123" t="s">
+        <v>86</v>
+      </c>
+      <c r="D123" t="s">
+        <v>31</v>
+      </c>
+      <c r="E123" t="s">
+        <v>41</v>
+      </c>
+      <c r="F123" t="s">
+        <v>33</v>
+      </c>
+      <c r="G123" t="s">
+        <v>54</v>
+      </c>
+      <c r="H123" t="s">
+        <v>35</v>
+      </c>
+      <c r="I123">
+        <v>154</v>
+      </c>
+      <c r="J123" t="s">
+        <v>40</v>
+      </c>
+      <c r="K123">
+        <v>1441</v>
+      </c>
+      <c r="L123">
+        <v>1.680083</v>
+      </c>
+      <c r="M123">
+        <v>11.40909091</v>
+      </c>
+      <c r="N123">
+        <v>160</v>
+      </c>
+      <c r="O123" t="s">
+        <v>36</v>
+      </c>
+      <c r="P123">
+        <v>1757</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>84</v>
+      </c>
+      <c r="R123">
+        <v>2421</v>
+      </c>
+      <c r="S123">
+        <v>725.73316799999998</v>
+      </c>
+      <c r="T123">
+        <v>154</v>
+      </c>
+      <c r="V123">
+        <v>11.409091</v>
+      </c>
+      <c r="W123">
+        <v>6.361008</v>
+      </c>
+      <c r="X123">
+        <v>185</v>
+      </c>
+      <c r="Y123">
+        <v>7.64147</v>
+      </c>
+      <c r="Z123">
+        <v>9.4972969999999997</v>
+      </c>
+    </row>
+    <row r="124" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>28</v>
+      </c>
+      <c r="B124" t="s">
+        <v>29</v>
+      </c>
+      <c r="C124" t="s">
+        <v>87</v>
+      </c>
+      <c r="D124" t="s">
+        <v>31</v>
+      </c>
+      <c r="E124" t="s">
+        <v>32</v>
+      </c>
+      <c r="F124" t="s">
+        <v>33</v>
+      </c>
+      <c r="G124" t="s">
+        <v>54</v>
+      </c>
+      <c r="H124" t="s">
+        <v>35</v>
+      </c>
+      <c r="I124">
+        <v>84</v>
+      </c>
+      <c r="J124" t="s">
+        <v>40</v>
+      </c>
+      <c r="K124">
+        <v>1670</v>
+      </c>
+      <c r="L124">
+        <v>1.3994009999999999</v>
+      </c>
+      <c r="M124">
+        <v>12.6547619</v>
+      </c>
+      <c r="N124" t="s">
+        <v>46</v>
+      </c>
+      <c r="O124">
+        <v>0</v>
+      </c>
+      <c r="P124">
+        <v>1063</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>88</v>
+      </c>
+      <c r="R124">
+        <v>2337</v>
+      </c>
+      <c r="S124">
+        <v>454.85665399999999</v>
+      </c>
+      <c r="T124">
+        <v>84</v>
+      </c>
+      <c r="V124">
+        <v>12.654762</v>
+      </c>
+      <c r="W124">
+        <v>3.5943520000000002</v>
+      </c>
+      <c r="X124">
+        <v>89</v>
+      </c>
+      <c r="Y124">
+        <v>3.8083010000000002</v>
+      </c>
+      <c r="Z124">
+        <v>11.943820000000001</v>
+      </c>
+    </row>
+    <row r="125" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>28</v>
+      </c>
+      <c r="B125" t="s">
+        <v>29</v>
+      </c>
+      <c r="C125" t="s">
+        <v>87</v>
+      </c>
+      <c r="D125" t="s">
+        <v>31</v>
+      </c>
+      <c r="E125" t="s">
+        <v>38</v>
+      </c>
+      <c r="F125" t="s">
+        <v>33</v>
+      </c>
+      <c r="G125" t="s">
+        <v>54</v>
+      </c>
+      <c r="H125" t="s">
+        <v>35</v>
+      </c>
+      <c r="I125">
+        <v>8</v>
+      </c>
+      <c r="J125" t="s">
+        <v>40</v>
+      </c>
+      <c r="K125">
+        <v>291</v>
+      </c>
+      <c r="L125">
+        <v>1.278351</v>
+      </c>
+      <c r="M125">
+        <v>13.5</v>
+      </c>
+      <c r="N125" t="s">
+        <v>46</v>
+      </c>
+      <c r="O125">
+        <v>0</v>
+      </c>
+      <c r="P125">
+        <v>108</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>88</v>
+      </c>
+      <c r="R125">
+        <v>372</v>
+      </c>
+      <c r="S125">
+        <v>290.32258100000001</v>
+      </c>
+      <c r="T125">
+        <v>8</v>
+      </c>
+      <c r="V125">
+        <v>13.5</v>
+      </c>
+      <c r="W125">
+        <v>2.1505380000000001</v>
+      </c>
+      <c r="X125">
+        <v>9</v>
+      </c>
+      <c r="Y125">
+        <v>2.4193549999999999</v>
+      </c>
+      <c r="Z125">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="126" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>28</v>
+      </c>
+      <c r="B126" t="s">
+        <v>29</v>
+      </c>
+      <c r="C126" t="s">
+        <v>87</v>
+      </c>
+      <c r="D126" t="s">
+        <v>31</v>
+      </c>
+      <c r="E126" t="s">
+        <v>51</v>
+      </c>
+      <c r="F126" t="s">
+        <v>33</v>
+      </c>
+      <c r="G126" t="s">
+        <v>54</v>
+      </c>
+      <c r="H126" t="s">
+        <v>35</v>
+      </c>
+      <c r="K126">
+        <v>33</v>
+      </c>
+      <c r="L126">
+        <v>1.212121</v>
+      </c>
+      <c r="N126" t="s">
+        <v>46</v>
+      </c>
+      <c r="O126">
+        <v>0</v>
+      </c>
+      <c r="P126">
+        <v>2</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>88</v>
+      </c>
+      <c r="R126">
+        <v>40</v>
+      </c>
+      <c r="S126">
+        <v>50</v>
+      </c>
+      <c r="X126">
+        <v>0</v>
+      </c>
+      <c r="Y126">
+        <v>0</v>
+      </c>
+      <c r="Z126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>28</v>
+      </c>
+      <c r="B127" t="s">
+        <v>29</v>
+      </c>
+      <c r="C127" t="s">
+        <v>87</v>
+      </c>
+      <c r="D127" t="s">
+        <v>31</v>
+      </c>
+      <c r="E127" t="s">
+        <v>39</v>
+      </c>
+      <c r="F127" t="s">
+        <v>33</v>
+      </c>
+      <c r="G127" t="s">
+        <v>54</v>
+      </c>
+      <c r="H127" t="s">
+        <v>35</v>
+      </c>
+      <c r="I127">
+        <v>53</v>
+      </c>
+      <c r="J127" t="s">
+        <v>40</v>
+      </c>
+      <c r="K127">
+        <v>1026</v>
+      </c>
+      <c r="L127">
+        <v>1.334308</v>
+      </c>
+      <c r="M127">
+        <v>13.566037740000001</v>
+      </c>
+      <c r="N127" t="s">
+        <v>46</v>
+      </c>
+      <c r="O127">
+        <v>0</v>
+      </c>
+      <c r="P127">
+        <v>719</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>88</v>
+      </c>
+      <c r="R127">
+        <v>1369</v>
+      </c>
+      <c r="S127">
+        <v>525.20087699999999</v>
+      </c>
+      <c r="T127">
+        <v>53</v>
+      </c>
+      <c r="V127">
+        <v>13.566038000000001</v>
+      </c>
+      <c r="W127">
+        <v>3.8714390000000001</v>
+      </c>
+      <c r="X127">
+        <v>70</v>
+      </c>
+      <c r="Y127">
+        <v>5.1132210000000002</v>
+      </c>
+      <c r="Z127">
+        <v>10.271428999999999</v>
+      </c>
+    </row>
+    <row r="128" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>28</v>
+      </c>
+      <c r="B128" t="s">
+        <v>29</v>
+      </c>
+      <c r="C128" t="s">
+        <v>87</v>
+      </c>
+      <c r="D128" t="s">
+        <v>31</v>
+      </c>
+      <c r="E128" t="s">
+        <v>41</v>
+      </c>
+      <c r="F128" t="s">
+        <v>33</v>
+      </c>
+      <c r="G128" t="s">
+        <v>54</v>
+      </c>
+      <c r="H128" t="s">
+        <v>35</v>
+      </c>
+      <c r="I128">
+        <v>67</v>
+      </c>
+      <c r="J128" t="s">
+        <v>40</v>
+      </c>
+      <c r="K128">
+        <v>971</v>
+      </c>
+      <c r="L128">
+        <v>1.3913489999999999</v>
+      </c>
+      <c r="M128">
+        <v>13.02985075</v>
+      </c>
+      <c r="N128" t="s">
+        <v>46</v>
+      </c>
+      <c r="O128">
+        <v>0</v>
+      </c>
+      <c r="P128">
+        <v>873</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>88</v>
+      </c>
+      <c r="R128">
+        <v>1351</v>
+      </c>
+      <c r="S128">
+        <v>646.18800899999997</v>
+      </c>
+      <c r="T128">
+        <v>67</v>
+      </c>
+      <c r="V128">
+        <v>13.029851000000001</v>
+      </c>
+      <c r="W128">
+        <v>4.9592890000000001</v>
+      </c>
+      <c r="X128">
+        <v>79</v>
+      </c>
+      <c r="Y128">
+        <v>5.8475200000000003</v>
+      </c>
+      <c r="Z128">
+        <v>11.050632999999999</v>
+      </c>
+    </row>
+    <row r="129" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>28</v>
+      </c>
+      <c r="B129" t="s">
+        <v>29</v>
+      </c>
+      <c r="C129" t="s">
+        <v>89</v>
+      </c>
+      <c r="D129" t="s">
+        <v>31</v>
+      </c>
+      <c r="E129" t="s">
+        <v>32</v>
+      </c>
+      <c r="F129" t="s">
+        <v>33</v>
+      </c>
+      <c r="G129" t="s">
+        <v>54</v>
+      </c>
+      <c r="H129" t="s">
+        <v>35</v>
+      </c>
+      <c r="I129">
+        <v>143</v>
+      </c>
+      <c r="J129" t="s">
+        <v>40</v>
+      </c>
+      <c r="K129">
+        <v>3152</v>
+      </c>
+      <c r="L129">
+        <v>1.3052029999999999</v>
+      </c>
+      <c r="M129">
+        <v>12.09090909</v>
+      </c>
+      <c r="N129" t="s">
+        <v>46</v>
+      </c>
+      <c r="O129">
+        <v>0</v>
+      </c>
+      <c r="P129">
+        <v>1729</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>88</v>
+      </c>
+      <c r="R129">
+        <v>4114</v>
+      </c>
+      <c r="S129">
+        <v>420.27224100000001</v>
+      </c>
+      <c r="T129">
+        <v>143</v>
+      </c>
+      <c r="V129">
+        <v>12.090909</v>
+      </c>
+      <c r="W129">
+        <v>3.4759359999999999</v>
+      </c>
+      <c r="X129">
+        <v>153</v>
+      </c>
+      <c r="Y129">
+        <v>3.7190080000000001</v>
+      </c>
+      <c r="Z129">
+        <v>11.300654</v>
+      </c>
+    </row>
+    <row r="130" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>28</v>
+      </c>
+      <c r="B130" t="s">
+        <v>29</v>
+      </c>
+      <c r="C130" t="s">
+        <v>89</v>
+      </c>
+      <c r="D130" t="s">
+        <v>31</v>
+      </c>
+      <c r="E130" t="s">
+        <v>32</v>
+      </c>
+      <c r="F130" t="s">
+        <v>75</v>
+      </c>
+      <c r="G130" t="s">
+        <v>54</v>
+      </c>
+      <c r="H130" t="s">
+        <v>35</v>
+      </c>
+      <c r="K130">
+        <v>1</v>
+      </c>
+      <c r="L130">
+        <v>2</v>
+      </c>
+      <c r="N130" t="s">
+        <v>46</v>
+      </c>
+      <c r="O130">
+        <v>0</v>
+      </c>
+      <c r="P130">
+        <v>1</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>88</v>
+      </c>
+      <c r="R130">
+        <v>2</v>
+      </c>
+      <c r="S130">
+        <v>500</v>
+      </c>
+      <c r="X130">
+        <v>0</v>
+      </c>
+      <c r="Y130">
+        <v>0</v>
+      </c>
+      <c r="Z130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>28</v>
+      </c>
+      <c r="B131" t="s">
+        <v>29</v>
+      </c>
+      <c r="C131" t="s">
+        <v>89</v>
+      </c>
+      <c r="D131" t="s">
+        <v>31</v>
+      </c>
+      <c r="E131" t="s">
+        <v>38</v>
+      </c>
+      <c r="F131" t="s">
+        <v>33</v>
+      </c>
+      <c r="G131" t="s">
+        <v>54</v>
+      </c>
+      <c r="H131" t="s">
+        <v>35</v>
+      </c>
+      <c r="I131">
+        <v>18</v>
+      </c>
+      <c r="J131" t="s">
+        <v>40</v>
+      </c>
+      <c r="K131">
+        <v>523</v>
+      </c>
+      <c r="L131">
+        <v>1.1892929999999999</v>
+      </c>
+      <c r="M131">
+        <v>10.33333333</v>
+      </c>
+      <c r="N131" t="s">
+        <v>46</v>
+      </c>
+      <c r="O131">
+        <v>0</v>
+      </c>
+      <c r="P131">
+        <v>186</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>88</v>
+      </c>
+      <c r="R131">
+        <v>622</v>
+      </c>
+      <c r="S131">
+        <v>299.03537</v>
+      </c>
+      <c r="T131">
+        <v>18</v>
+      </c>
+      <c r="V131">
+        <v>10.333333</v>
+      </c>
+      <c r="W131">
+        <v>2.893891</v>
+      </c>
+      <c r="X131">
+        <v>19</v>
+      </c>
+      <c r="Y131">
+        <v>3.054662</v>
+      </c>
+      <c r="Z131">
+        <v>9.7894740000000002</v>
+      </c>
+    </row>
+    <row r="132" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>28</v>
+      </c>
+      <c r="B132" t="s">
+        <v>29</v>
+      </c>
+      <c r="C132" t="s">
+        <v>89</v>
+      </c>
+      <c r="D132" t="s">
+        <v>31</v>
+      </c>
+      <c r="E132" t="s">
+        <v>51</v>
+      </c>
+      <c r="F132" t="s">
+        <v>33</v>
+      </c>
+      <c r="G132" t="s">
+        <v>54</v>
+      </c>
+      <c r="H132" t="s">
+        <v>35</v>
+      </c>
+      <c r="K132">
+        <v>29</v>
+      </c>
+      <c r="L132">
+        <v>1.034483</v>
+      </c>
+      <c r="N132" t="s">
+        <v>46</v>
+      </c>
+      <c r="O132">
+        <v>0</v>
+      </c>
+      <c r="P132">
+        <v>1</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>88</v>
+      </c>
+      <c r="R132">
+        <v>30</v>
+      </c>
+      <c r="S132">
+        <v>33.333333000000003</v>
+      </c>
+      <c r="X132">
+        <v>0</v>
+      </c>
+      <c r="Y132">
+        <v>0</v>
+      </c>
+      <c r="Z132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>28</v>
+      </c>
+      <c r="B133" t="s">
+        <v>29</v>
+      </c>
+      <c r="C133" t="s">
+        <v>89</v>
+      </c>
+      <c r="D133" t="s">
+        <v>31</v>
+      </c>
+      <c r="E133" t="s">
+        <v>39</v>
+      </c>
+      <c r="F133" t="s">
+        <v>33</v>
+      </c>
+      <c r="G133" t="s">
+        <v>54</v>
+      </c>
+      <c r="H133" t="s">
+        <v>35</v>
+      </c>
+      <c r="I133">
+        <v>27</v>
+      </c>
+      <c r="J133" t="s">
+        <v>40</v>
+      </c>
+      <c r="K133">
+        <v>709</v>
+      </c>
+      <c r="L133">
+        <v>1.1664319999999999</v>
+      </c>
+      <c r="M133">
+        <v>13.777777779999999</v>
+      </c>
+      <c r="N133" t="s">
+        <v>46</v>
+      </c>
+      <c r="O133">
+        <v>0</v>
+      </c>
+      <c r="P133">
+        <v>372</v>
+      </c>
+      <c r="Q133" t="s">
+        <v>88</v>
+      </c>
+      <c r="R133">
+        <v>827</v>
+      </c>
+      <c r="S133">
+        <v>449.818622</v>
+      </c>
+      <c r="T133">
+        <v>27</v>
+      </c>
+      <c r="V133">
+        <v>13.777778</v>
+      </c>
+      <c r="W133">
+        <v>3.2648130000000002</v>
+      </c>
+      <c r="X133">
+        <v>30</v>
+      </c>
+      <c r="Y133">
+        <v>3.62757</v>
+      </c>
+      <c r="Z133">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>28</v>
+      </c>
+      <c r="B134" t="s">
+        <v>29</v>
+      </c>
+      <c r="C134" t="s">
+        <v>89</v>
+      </c>
+      <c r="D134" t="s">
+        <v>31</v>
+      </c>
+      <c r="E134" t="s">
+        <v>41</v>
+      </c>
+      <c r="F134" t="s">
+        <v>33</v>
+      </c>
+      <c r="G134" t="s">
+        <v>54</v>
+      </c>
+      <c r="H134" t="s">
+        <v>35</v>
+      </c>
+      <c r="I134">
+        <v>33</v>
+      </c>
+      <c r="J134" t="s">
+        <v>40</v>
+      </c>
+      <c r="K134">
+        <v>632</v>
+      </c>
+      <c r="L134">
+        <v>1.2310129999999999</v>
+      </c>
+      <c r="M134">
+        <v>14.030303030000001</v>
+      </c>
+      <c r="N134" t="s">
+        <v>46</v>
+      </c>
+      <c r="O134">
+        <v>0</v>
+      </c>
+      <c r="P134">
+        <v>463</v>
+      </c>
+      <c r="Q134" t="s">
+        <v>88</v>
+      </c>
+      <c r="R134">
+        <v>778</v>
+      </c>
+      <c r="S134">
+        <v>595.115681</v>
+      </c>
+      <c r="T134">
+        <v>33</v>
+      </c>
+      <c r="V134">
+        <v>14.030303</v>
+      </c>
+      <c r="W134">
+        <v>4.2416450000000001</v>
+      </c>
+      <c r="X134">
+        <v>39</v>
+      </c>
+      <c r="Y134">
+        <v>5.0128529999999998</v>
+      </c>
+      <c r="Z134">
+        <v>11.871795000000001</v>
+      </c>
+    </row>
+    <row r="135" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>28</v>
+      </c>
+      <c r="B135" t="s">
+        <v>29</v>
+      </c>
+      <c r="C135" t="s">
+        <v>90</v>
+      </c>
+      <c r="D135" t="s">
+        <v>31</v>
+      </c>
+      <c r="E135" t="s">
+        <v>32</v>
+      </c>
+      <c r="F135" t="s">
+        <v>33</v>
+      </c>
+      <c r="G135" t="s">
+        <v>54</v>
+      </c>
+      <c r="H135" t="s">
+        <v>35</v>
+      </c>
+      <c r="I135">
+        <v>32</v>
+      </c>
+      <c r="J135" t="s">
+        <v>40</v>
+      </c>
+      <c r="K135">
+        <v>884</v>
+      </c>
+      <c r="L135">
+        <v>1.3382350000000001</v>
+      </c>
+      <c r="M135">
+        <v>23.71875</v>
+      </c>
+      <c r="N135" t="s">
+        <v>46</v>
+      </c>
+      <c r="O135">
+        <v>0</v>
+      </c>
+      <c r="P135">
+        <v>759</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>47</v>
+      </c>
+      <c r="R135">
+        <v>1183</v>
+      </c>
+      <c r="S135">
+        <v>641.58918000000006</v>
+      </c>
+      <c r="T135">
+        <v>32</v>
+      </c>
+      <c r="V135">
+        <v>23.71875</v>
+      </c>
+      <c r="W135">
+        <v>2.704987</v>
+      </c>
+      <c r="X135">
+        <v>44</v>
+      </c>
+      <c r="Y135">
+        <v>3.7193580000000002</v>
+      </c>
+      <c r="Z135">
+        <v>17.25</v>
+      </c>
+    </row>
+    <row r="136" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>28</v>
+      </c>
+      <c r="B136" t="s">
+        <v>29</v>
+      </c>
+      <c r="C136" t="s">
+        <v>90</v>
+      </c>
+      <c r="D136" t="s">
+        <v>31</v>
+      </c>
+      <c r="E136" t="s">
+        <v>38</v>
+      </c>
+      <c r="F136" t="s">
+        <v>33</v>
+      </c>
+      <c r="G136" t="s">
+        <v>54</v>
+      </c>
+      <c r="H136" t="s">
+        <v>35</v>
+      </c>
+      <c r="I136">
+        <v>3</v>
+      </c>
+      <c r="J136" t="s">
+        <v>40</v>
+      </c>
+      <c r="K136">
+        <v>145</v>
+      </c>
+      <c r="L136">
+        <v>1.2758620000000001</v>
+      </c>
+      <c r="M136">
+        <v>31.333333329999999</v>
+      </c>
+      <c r="N136" t="s">
+        <v>46</v>
+      </c>
+      <c r="O136">
+        <v>0</v>
+      </c>
+      <c r="P136">
+        <v>94</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>47</v>
+      </c>
+      <c r="R136">
+        <v>185</v>
+      </c>
+      <c r="S136">
+        <v>508.10810800000002</v>
+      </c>
+      <c r="T136">
+        <v>3</v>
+      </c>
+      <c r="V136">
+        <v>31.333333</v>
+      </c>
+      <c r="W136">
+        <v>1.6216219999999999</v>
+      </c>
+      <c r="X136">
+        <v>4</v>
+      </c>
+      <c r="Y136">
+        <v>2.1621619999999999</v>
+      </c>
+      <c r="Z136">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>28</v>
+      </c>
+      <c r="B137" t="s">
+        <v>29</v>
+      </c>
+      <c r="C137" t="s">
+        <v>90</v>
+      </c>
+      <c r="D137" t="s">
+        <v>31</v>
+      </c>
+      <c r="E137" t="s">
+        <v>51</v>
+      </c>
+      <c r="F137" t="s">
+        <v>33</v>
+      </c>
+      <c r="G137" t="s">
+        <v>54</v>
+      </c>
+      <c r="H137" t="s">
+        <v>35</v>
+      </c>
+      <c r="K137">
+        <v>23</v>
+      </c>
+      <c r="L137">
+        <v>1</v>
+      </c>
+      <c r="N137" t="s">
+        <v>46</v>
+      </c>
+      <c r="O137">
+        <v>0</v>
+      </c>
+      <c r="P137">
+        <v>3</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>47</v>
+      </c>
+      <c r="R137">
+        <v>23</v>
+      </c>
+      <c r="S137">
+        <v>130.43478300000001</v>
+      </c>
+      <c r="X137">
+        <v>1</v>
+      </c>
+      <c r="Y137">
+        <v>4.3478260000000004</v>
+      </c>
+      <c r="Z137">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>28</v>
+      </c>
+      <c r="B138" t="s">
+        <v>29</v>
+      </c>
+      <c r="C138" t="s">
+        <v>90</v>
+      </c>
+      <c r="D138" t="s">
+        <v>31</v>
+      </c>
+      <c r="E138" t="s">
+        <v>39</v>
+      </c>
+      <c r="F138" t="s">
+        <v>33</v>
+      </c>
+      <c r="G138" t="s">
+        <v>54</v>
+      </c>
+      <c r="H138" t="s">
+        <v>35</v>
+      </c>
+      <c r="I138">
+        <v>44</v>
+      </c>
+      <c r="J138" t="s">
+        <v>40</v>
+      </c>
+      <c r="K138">
+        <v>1274</v>
+      </c>
+      <c r="L138">
+        <v>1.2551019999999999</v>
+      </c>
+      <c r="M138">
+        <v>23.636363639999999</v>
+      </c>
+      <c r="N138" t="s">
+        <v>46</v>
+      </c>
+      <c r="O138">
+        <v>0</v>
+      </c>
+      <c r="P138">
+        <v>1040</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>47</v>
+      </c>
+      <c r="R138">
+        <v>1599</v>
+      </c>
+      <c r="S138">
+        <v>650.40650400000004</v>
+      </c>
+      <c r="T138">
+        <v>44</v>
+      </c>
+      <c r="V138">
+        <v>23.636364</v>
+      </c>
+      <c r="W138">
+        <v>2.7517200000000002</v>
+      </c>
+      <c r="X138">
+        <v>74</v>
+      </c>
+      <c r="Y138">
+        <v>4.6278920000000001</v>
+      </c>
+      <c r="Z138">
+        <v>14.054054000000001</v>
+      </c>
+    </row>
+    <row r="139" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>28</v>
+      </c>
+      <c r="B139" t="s">
+        <v>29</v>
+      </c>
+      <c r="C139" t="s">
+        <v>90</v>
+      </c>
+      <c r="D139" t="s">
+        <v>31</v>
+      </c>
+      <c r="E139" t="s">
+        <v>41</v>
+      </c>
+      <c r="F139" t="s">
+        <v>33</v>
+      </c>
+      <c r="G139" t="s">
+        <v>54</v>
+      </c>
+      <c r="H139" t="s">
+        <v>35</v>
+      </c>
+      <c r="I139">
+        <v>27</v>
+      </c>
+      <c r="J139" t="s">
+        <v>40</v>
+      </c>
+      <c r="K139">
+        <v>845</v>
+      </c>
+      <c r="L139">
+        <v>1.3514790000000001</v>
+      </c>
+      <c r="M139">
+        <v>36.370370370000003</v>
+      </c>
+      <c r="N139" t="s">
+        <v>46</v>
+      </c>
+      <c r="O139">
+        <v>0</v>
+      </c>
+      <c r="P139">
+        <v>982</v>
+      </c>
+      <c r="Q139" t="s">
+        <v>47</v>
+      </c>
+      <c r="R139">
+        <v>1142</v>
+      </c>
+      <c r="S139">
+        <v>859.89492099999995</v>
+      </c>
+      <c r="T139">
+        <v>27</v>
+      </c>
+      <c r="V139">
+        <v>36.370370000000001</v>
+      </c>
+      <c r="W139">
+        <v>2.3642729999999998</v>
+      </c>
+      <c r="X139">
+        <v>34</v>
+      </c>
+      <c r="Y139">
+        <v>2.977233</v>
+      </c>
+      <c r="Z139">
+        <v>28.882352999999998</v>
+      </c>
+    </row>
+    <row r="140" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>28</v>
+      </c>
+      <c r="B140" t="s">
+        <v>29</v>
+      </c>
+      <c r="C140" t="s">
+        <v>91</v>
+      </c>
+      <c r="D140" t="s">
+        <v>31</v>
+      </c>
+      <c r="E140" t="s">
+        <v>32</v>
+      </c>
+      <c r="F140" t="s">
+        <v>33</v>
+      </c>
+      <c r="G140" t="s">
+        <v>54</v>
+      </c>
+      <c r="H140" t="s">
+        <v>35</v>
+      </c>
+      <c r="I140">
+        <v>12</v>
+      </c>
+      <c r="J140" t="s">
+        <v>40</v>
+      </c>
+      <c r="K140">
+        <v>724</v>
+      </c>
+      <c r="L140">
+        <v>1.390884</v>
+      </c>
+      <c r="M140">
+        <v>56.583333330000002</v>
+      </c>
+      <c r="N140" t="s">
+        <v>46</v>
+      </c>
+      <c r="O140">
+        <v>0</v>
+      </c>
+      <c r="P140">
+        <v>679</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>88</v>
+      </c>
+      <c r="R140">
+        <v>1007</v>
+      </c>
+      <c r="S140">
+        <v>674.28003999999999</v>
+      </c>
+      <c r="T140">
+        <v>12</v>
+      </c>
+      <c r="V140">
+        <v>56.583333000000003</v>
+      </c>
+      <c r="W140">
+        <v>1.1916580000000001</v>
+      </c>
+      <c r="X140">
+        <v>12</v>
+      </c>
+      <c r="Y140">
+        <v>1.1916580000000001</v>
+      </c>
+      <c r="Z140">
+        <v>56.583333000000003</v>
+      </c>
+    </row>
+    <row r="141" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>28</v>
+      </c>
+      <c r="B141" t="s">
+        <v>29</v>
+      </c>
+      <c r="C141" t="s">
+        <v>91</v>
+      </c>
+      <c r="D141" t="s">
+        <v>31</v>
+      </c>
+      <c r="E141" t="s">
+        <v>38</v>
+      </c>
+      <c r="F141" t="s">
+        <v>33</v>
+      </c>
+      <c r="G141" t="s">
+        <v>54</v>
+      </c>
+      <c r="H141" t="s">
+        <v>35</v>
+      </c>
+      <c r="I141">
+        <v>2</v>
+      </c>
+      <c r="J141" t="s">
+        <v>40</v>
+      </c>
+      <c r="K141">
+        <v>178</v>
+      </c>
+      <c r="L141">
+        <v>1.342697</v>
+      </c>
+      <c r="M141">
+        <v>48</v>
+      </c>
+      <c r="N141" t="s">
+        <v>46</v>
+      </c>
+      <c r="O141">
+        <v>0</v>
+      </c>
+      <c r="P141">
+        <v>96</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>88</v>
+      </c>
+      <c r="R141">
+        <v>239</v>
+      </c>
+      <c r="S141">
+        <v>401.67363999999998</v>
+      </c>
+      <c r="T141">
+        <v>2</v>
+      </c>
+      <c r="V141">
+        <v>48</v>
+      </c>
+      <c r="W141">
+        <v>0.83682000000000001</v>
+      </c>
+      <c r="X141">
+        <v>2</v>
+      </c>
+      <c r="Y141">
+        <v>0.83682000000000001</v>
+      </c>
+      <c r="Z141">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="142" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>28</v>
+      </c>
+      <c r="B142" t="s">
+        <v>29</v>
+      </c>
+      <c r="C142" t="s">
+        <v>91</v>
+      </c>
+      <c r="D142" t="s">
+        <v>31</v>
+      </c>
+      <c r="E142" t="s">
+        <v>39</v>
+      </c>
+      <c r="F142" t="s">
+        <v>33</v>
+      </c>
+      <c r="G142" t="s">
+        <v>54</v>
+      </c>
+      <c r="H142" t="s">
+        <v>35</v>
+      </c>
+      <c r="I142">
+        <v>28</v>
+      </c>
+      <c r="J142" t="s">
+        <v>40</v>
+      </c>
+      <c r="K142">
+        <v>747</v>
+      </c>
+      <c r="L142">
+        <v>1.364123</v>
+      </c>
+      <c r="M142">
+        <v>27.178571430000002</v>
+      </c>
+      <c r="N142" t="s">
+        <v>46</v>
+      </c>
+      <c r="O142">
+        <v>0</v>
+      </c>
+      <c r="P142">
+        <v>761</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>88</v>
+      </c>
+      <c r="R142">
+        <v>1019</v>
+      </c>
+      <c r="S142">
+        <v>746.81059900000002</v>
+      </c>
+      <c r="T142">
+        <v>28</v>
+      </c>
+      <c r="V142">
+        <v>27.178571000000002</v>
+      </c>
+      <c r="W142">
+        <v>2.747792</v>
+      </c>
+      <c r="X142">
+        <v>33</v>
+      </c>
+      <c r="Y142">
+        <v>3.2384689999999998</v>
+      </c>
+      <c r="Z142">
+        <v>23.060606</v>
+      </c>
+    </row>
+    <row r="143" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>28</v>
+      </c>
+      <c r="B143" t="s">
+        <v>29</v>
+      </c>
+      <c r="C143" t="s">
+        <v>91</v>
+      </c>
+      <c r="D143" t="s">
+        <v>31</v>
+      </c>
+      <c r="E143" t="s">
+        <v>41</v>
+      </c>
+      <c r="F143" t="s">
+        <v>33</v>
+      </c>
+      <c r="G143" t="s">
+        <v>54</v>
+      </c>
+      <c r="H143" t="s">
+        <v>35</v>
+      </c>
+      <c r="I143">
+        <v>46</v>
+      </c>
+      <c r="J143" t="s">
+        <v>40</v>
+      </c>
+      <c r="K143">
+        <v>813</v>
+      </c>
+      <c r="L143">
+        <v>1.516605</v>
+      </c>
+      <c r="M143">
+        <v>30.217391299999999</v>
+      </c>
+      <c r="N143" t="s">
+        <v>46</v>
+      </c>
+      <c r="O143">
+        <v>0</v>
+      </c>
+      <c r="P143">
+        <v>1390</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>88</v>
+      </c>
+      <c r="R143">
+        <v>1233</v>
+      </c>
+      <c r="S143">
+        <v>1127.331711</v>
+      </c>
+      <c r="T143">
+        <v>46</v>
+      </c>
+      <c r="V143">
+        <v>30.217390999999999</v>
+      </c>
+      <c r="W143">
+        <v>3.7307380000000001</v>
+      </c>
+      <c r="X143">
+        <v>55</v>
+      </c>
+      <c r="Y143">
+        <v>4.4606649999999997</v>
+      </c>
+      <c r="Z143">
+        <v>25.272727</v>
+      </c>
+    </row>
+    <row r="144" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>28</v>
+      </c>
+      <c r="B144" t="s">
+        <v>29</v>
+      </c>
+      <c r="C144" t="s">
+        <v>92</v>
+      </c>
+      <c r="D144" t="s">
+        <v>31</v>
+      </c>
+      <c r="E144" t="s">
+        <v>32</v>
+      </c>
+      <c r="F144" t="s">
+        <v>33</v>
+      </c>
+      <c r="G144" t="s">
+        <v>54</v>
+      </c>
+      <c r="H144" t="s">
+        <v>35</v>
+      </c>
+      <c r="I144">
+        <v>33</v>
+      </c>
+      <c r="J144" t="s">
+        <v>40</v>
+      </c>
+      <c r="K144">
+        <v>423</v>
+      </c>
+      <c r="L144">
+        <v>1.401891</v>
+      </c>
+      <c r="M144">
+        <v>8.7878787900000006</v>
+      </c>
+      <c r="N144" t="s">
+        <v>46</v>
+      </c>
+      <c r="O144">
+        <v>0</v>
+      </c>
+      <c r="P144">
+        <v>290</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>47</v>
+      </c>
+      <c r="R144">
+        <v>593</v>
+      </c>
+      <c r="S144">
+        <v>489.03878600000002</v>
+      </c>
+      <c r="T144">
+        <v>33</v>
+      </c>
+      <c r="V144">
+        <v>8.7878790000000002</v>
+      </c>
+      <c r="W144">
+        <v>5.5649240000000004</v>
+      </c>
+      <c r="X144">
+        <v>35</v>
+      </c>
+      <c r="Y144">
+        <v>5.9021920000000003</v>
+      </c>
+      <c r="Z144">
+        <v>8.2857140000000005</v>
+      </c>
+    </row>
+    <row r="145" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>28</v>
+      </c>
+      <c r="B145" t="s">
+        <v>29</v>
+      </c>
+      <c r="C145" t="s">
+        <v>92</v>
+      </c>
+      <c r="D145" t="s">
+        <v>31</v>
+      </c>
+      <c r="E145" t="s">
+        <v>38</v>
+      </c>
+      <c r="F145" t="s">
+        <v>33</v>
+      </c>
+      <c r="G145" t="s">
+        <v>54</v>
+      </c>
+      <c r="H145" t="s">
+        <v>35</v>
+      </c>
+      <c r="I145">
+        <v>2</v>
+      </c>
+      <c r="J145" t="s">
+        <v>40</v>
+      </c>
+      <c r="K145">
+        <v>49</v>
+      </c>
+      <c r="L145">
+        <v>1.2244900000000001</v>
+      </c>
+      <c r="M145">
+        <v>12</v>
+      </c>
+      <c r="N145" t="s">
+        <v>46</v>
+      </c>
+      <c r="O145">
+        <v>0</v>
+      </c>
+      <c r="P145">
+        <v>24</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>47</v>
+      </c>
+      <c r="R145">
+        <v>60</v>
+      </c>
+      <c r="S145">
+        <v>400</v>
+      </c>
+      <c r="T145">
+        <v>2</v>
+      </c>
+      <c r="V145">
+        <v>12</v>
+      </c>
+      <c r="W145">
+        <v>3.3333330000000001</v>
+      </c>
+      <c r="X145">
+        <v>2</v>
+      </c>
+      <c r="Y145">
+        <v>3.3333330000000001</v>
+      </c>
+      <c r="Z145">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="146" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>28</v>
+      </c>
+      <c r="B146" t="s">
+        <v>29</v>
+      </c>
+      <c r="C146" t="s">
+        <v>92</v>
+      </c>
+      <c r="D146" t="s">
+        <v>31</v>
+      </c>
+      <c r="E146" t="s">
+        <v>51</v>
+      </c>
+      <c r="F146" t="s">
+        <v>33</v>
+      </c>
+      <c r="G146" t="s">
+        <v>54</v>
+      </c>
+      <c r="H146" t="s">
+        <v>35</v>
+      </c>
+      <c r="K146">
+        <v>12</v>
+      </c>
+      <c r="L146">
+        <v>1</v>
+      </c>
+      <c r="N146" t="s">
+        <v>46</v>
+      </c>
+      <c r="O146">
+        <v>0</v>
+      </c>
+      <c r="P146">
+        <v>0</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>47</v>
+      </c>
+      <c r="R146">
+        <v>12</v>
+      </c>
+      <c r="S146">
+        <v>0</v>
+      </c>
+      <c r="X146">
+        <v>0</v>
+      </c>
+      <c r="Y146">
+        <v>0</v>
+      </c>
+      <c r="Z146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>28</v>
+      </c>
+      <c r="B147" t="s">
+        <v>29</v>
+      </c>
+      <c r="C147" t="s">
+        <v>92</v>
+      </c>
+      <c r="D147" t="s">
+        <v>31</v>
+      </c>
+      <c r="E147" t="s">
+        <v>39</v>
+      </c>
+      <c r="F147" t="s">
+        <v>33</v>
+      </c>
+      <c r="G147" t="s">
+        <v>54</v>
+      </c>
+      <c r="H147" t="s">
+        <v>35</v>
+      </c>
+      <c r="I147">
+        <v>8</v>
+      </c>
+      <c r="J147" t="s">
+        <v>40</v>
+      </c>
+      <c r="K147">
+        <v>88</v>
+      </c>
+      <c r="L147">
+        <v>1.318182</v>
+      </c>
+      <c r="M147">
+        <v>9.25</v>
+      </c>
+      <c r="N147" t="s">
+        <v>46</v>
+      </c>
+      <c r="O147">
+        <v>0</v>
+      </c>
+      <c r="P147">
+        <v>74</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>47</v>
+      </c>
+      <c r="R147">
+        <v>116</v>
+      </c>
+      <c r="S147">
+        <v>637.93103399999995</v>
+      </c>
+      <c r="T147">
+        <v>8</v>
+      </c>
+      <c r="V147">
+        <v>9.25</v>
+      </c>
+      <c r="W147">
+        <v>6.8965519999999998</v>
+      </c>
+      <c r="X147">
+        <v>10</v>
+      </c>
+      <c r="Y147">
+        <v>8.6206899999999997</v>
+      </c>
+      <c r="Z147">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>28</v>
+      </c>
+      <c r="B148" t="s">
+        <v>29</v>
+      </c>
+      <c r="C148" t="s">
+        <v>92</v>
+      </c>
+      <c r="D148" t="s">
+        <v>31</v>
+      </c>
+      <c r="E148" t="s">
+        <v>41</v>
+      </c>
+      <c r="F148" t="s">
+        <v>33</v>
+      </c>
+      <c r="G148" t="s">
+        <v>54</v>
+      </c>
+      <c r="H148" t="s">
+        <v>35</v>
+      </c>
+      <c r="I148">
+        <v>254</v>
+      </c>
+      <c r="J148" t="s">
+        <v>40</v>
+      </c>
+      <c r="K148">
+        <v>3166</v>
+      </c>
+      <c r="L148">
+        <v>1.4295640000000001</v>
+      </c>
+      <c r="M148">
+        <v>9.3267716499999995</v>
+      </c>
+      <c r="N148" t="s">
+        <v>46</v>
+      </c>
+      <c r="O148">
+        <v>0</v>
+      </c>
+      <c r="P148">
+        <v>2369</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>47</v>
+      </c>
+      <c r="R148">
+        <v>4526</v>
+      </c>
+      <c r="S148">
+        <v>523.42023900000004</v>
+      </c>
+      <c r="T148">
+        <v>254</v>
+      </c>
+      <c r="V148">
+        <v>9.3267720000000001</v>
+      </c>
+      <c r="W148">
+        <v>5.6120190000000001</v>
+      </c>
+      <c r="X148">
+        <v>293</v>
+      </c>
+      <c r="Y148">
+        <v>6.4737070000000001</v>
+      </c>
+      <c r="Z148">
+        <v>8.085324</v>
+      </c>
+    </row>
+    <row r="149" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>28</v>
+      </c>
+      <c r="B149" t="s">
+        <v>29</v>
+      </c>
+      <c r="C149" t="s">
+        <v>93</v>
+      </c>
+      <c r="D149" t="s">
+        <v>31</v>
+      </c>
+      <c r="E149" t="s">
+        <v>32</v>
+      </c>
+      <c r="F149" t="s">
+        <v>33</v>
+      </c>
+      <c r="G149" t="s">
+        <v>54</v>
+      </c>
+      <c r="H149" t="s">
+        <v>35</v>
+      </c>
+      <c r="I149">
+        <v>36</v>
+      </c>
+      <c r="J149" t="s">
+        <v>40</v>
+      </c>
+      <c r="K149">
+        <v>989</v>
+      </c>
+      <c r="L149">
+        <v>1.517695</v>
+      </c>
+      <c r="M149">
+        <v>19.61111111</v>
+      </c>
+      <c r="N149" t="s">
+        <v>46</v>
+      </c>
+      <c r="O149">
+        <v>0</v>
+      </c>
+      <c r="P149">
+        <v>706</v>
+      </c>
+      <c r="Q149" t="s">
+        <v>47</v>
+      </c>
+      <c r="R149">
+        <v>1501</v>
+      </c>
+      <c r="S149">
+        <v>470.35309799999999</v>
+      </c>
+      <c r="T149">
+        <v>36</v>
+      </c>
+      <c r="V149">
+        <v>19.611111000000001</v>
+      </c>
+      <c r="W149">
+        <v>2.3984009999999998</v>
+      </c>
+      <c r="X149">
+        <v>42</v>
+      </c>
+      <c r="Y149">
+        <v>2.7981349999999998</v>
+      </c>
+      <c r="Z149">
+        <v>16.809524</v>
+      </c>
+    </row>
+    <row r="150" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>28</v>
+      </c>
+      <c r="B150" t="s">
+        <v>29</v>
+      </c>
+      <c r="C150" t="s">
+        <v>93</v>
+      </c>
+      <c r="D150" t="s">
+        <v>31</v>
+      </c>
+      <c r="E150" t="s">
+        <v>38</v>
+      </c>
+      <c r="F150" t="s">
+        <v>33</v>
+      </c>
+      <c r="G150" t="s">
+        <v>54</v>
+      </c>
+      <c r="H150" t="s">
+        <v>35</v>
+      </c>
+      <c r="K150">
+        <v>51</v>
+      </c>
+      <c r="L150">
+        <v>1.2941180000000001</v>
+      </c>
+      <c r="N150" t="s">
+        <v>46</v>
+      </c>
+      <c r="O150">
+        <v>0</v>
+      </c>
+      <c r="P150">
+        <v>25</v>
+      </c>
+      <c r="Q150" t="s">
+        <v>47</v>
+      </c>
+      <c r="R150">
+        <v>66</v>
+      </c>
+      <c r="S150">
+        <v>378.78787899999998</v>
+      </c>
+      <c r="X150">
+        <v>0</v>
+      </c>
+      <c r="Y150">
+        <v>0</v>
+      </c>
+      <c r="Z150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>28</v>
+      </c>
+      <c r="B151" t="s">
+        <v>29</v>
+      </c>
+      <c r="C151" t="s">
+        <v>93</v>
+      </c>
+      <c r="D151" t="s">
+        <v>31</v>
+      </c>
+      <c r="E151" t="s">
+        <v>39</v>
+      </c>
+      <c r="F151" t="s">
+        <v>33</v>
+      </c>
+      <c r="G151" t="s">
+        <v>54</v>
+      </c>
+      <c r="H151" t="s">
+        <v>35</v>
+      </c>
+      <c r="I151">
+        <v>109</v>
+      </c>
+      <c r="J151" t="s">
+        <v>40</v>
+      </c>
+      <c r="K151">
+        <v>1932</v>
+      </c>
+      <c r="L151">
+        <v>1.4466870000000001</v>
+      </c>
+      <c r="M151">
+        <v>15.57798165</v>
+      </c>
+      <c r="N151" t="s">
+        <v>46</v>
+      </c>
+      <c r="O151">
+        <v>0</v>
+      </c>
+      <c r="P151">
+        <v>1698</v>
+      </c>
+      <c r="Q151" t="s">
+        <v>47</v>
+      </c>
+      <c r="R151">
+        <v>2795</v>
+      </c>
+      <c r="S151">
+        <v>607.513417</v>
+      </c>
+      <c r="T151">
+        <v>109</v>
+      </c>
+      <c r="V151">
+        <v>15.577982</v>
+      </c>
+      <c r="W151">
+        <v>3.8998210000000002</v>
+      </c>
+      <c r="X151">
+        <v>138</v>
+      </c>
+      <c r="Y151">
+        <v>4.9373880000000003</v>
+      </c>
+      <c r="Z151">
+        <v>12.304347999999999</v>
+      </c>
+    </row>
+    <row r="152" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>28</v>
+      </c>
+      <c r="B152" t="s">
+        <v>29</v>
+      </c>
+      <c r="C152" t="s">
+        <v>93</v>
+      </c>
+      <c r="D152" t="s">
+        <v>31</v>
+      </c>
+      <c r="E152" t="s">
+        <v>41</v>
+      </c>
+      <c r="F152" t="s">
+        <v>33</v>
+      </c>
+      <c r="G152" t="s">
+        <v>54</v>
+      </c>
+      <c r="H152" t="s">
+        <v>35</v>
+      </c>
+      <c r="I152">
+        <v>21</v>
+      </c>
+      <c r="J152" t="s">
+        <v>40</v>
+      </c>
+      <c r="K152">
+        <v>459</v>
+      </c>
+      <c r="L152">
+        <v>1.3289759999999999</v>
+      </c>
+      <c r="M152">
+        <v>19.333333329999999</v>
+      </c>
+      <c r="N152" t="s">
+        <v>46</v>
+      </c>
+      <c r="O152">
+        <v>0</v>
+      </c>
+      <c r="P152">
+        <v>406</v>
+      </c>
+      <c r="Q152" t="s">
+        <v>47</v>
+      </c>
+      <c r="R152">
+        <v>610</v>
+      </c>
+      <c r="S152">
+        <v>665.57376999999997</v>
+      </c>
+      <c r="T152">
+        <v>21</v>
+      </c>
+      <c r="V152">
+        <v>19.333333</v>
+      </c>
+      <c r="W152">
+        <v>3.4426230000000002</v>
+      </c>
+      <c r="X152">
+        <v>27</v>
+      </c>
+      <c r="Y152">
+        <v>4.4262300000000003</v>
+      </c>
+      <c r="Z152">
+        <v>15.037037</v>
+      </c>
+    </row>
+    <row r="153" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>28</v>
+      </c>
+      <c r="B153" t="s">
+        <v>29</v>
+      </c>
+      <c r="C153" t="s">
+        <v>94</v>
+      </c>
+      <c r="D153" t="s">
+        <v>31</v>
+      </c>
+      <c r="E153" t="s">
+        <v>32</v>
+      </c>
+      <c r="F153" t="s">
+        <v>33</v>
+      </c>
+      <c r="G153" t="s">
+        <v>54</v>
+      </c>
+      <c r="H153" t="s">
+        <v>35</v>
+      </c>
+      <c r="I153">
+        <v>108</v>
+      </c>
+      <c r="J153" t="s">
+        <v>40</v>
+      </c>
+      <c r="K153">
+        <v>2741</v>
+      </c>
+      <c r="L153">
+        <v>1.5457860000000001</v>
+      </c>
+      <c r="M153">
+        <v>18.564814810000001</v>
+      </c>
+      <c r="N153" t="s">
+        <v>46</v>
+      </c>
+      <c r="O153">
+        <v>0</v>
+      </c>
+      <c r="P153">
+        <v>2005</v>
+      </c>
+      <c r="Q153" t="s">
+        <v>47</v>
+      </c>
+      <c r="R153">
+        <v>4237</v>
+      </c>
+      <c r="S153">
+        <v>473.21217799999999</v>
+      </c>
+      <c r="T153">
+        <v>108</v>
+      </c>
+      <c r="V153">
+        <v>18.564814999999999</v>
+      </c>
+      <c r="W153">
+        <v>2.5489730000000002</v>
+      </c>
+      <c r="X153">
+        <v>127</v>
+      </c>
+      <c r="Y153">
+        <v>2.997404</v>
+      </c>
+      <c r="Z153">
+        <v>15.787402</v>
+      </c>
+    </row>
+    <row r="154" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>28</v>
+      </c>
+      <c r="B154" t="s">
+        <v>29</v>
+      </c>
+      <c r="C154" t="s">
+        <v>94</v>
+      </c>
+      <c r="D154" t="s">
+        <v>31</v>
+      </c>
+      <c r="E154" t="s">
+        <v>38</v>
+      </c>
+      <c r="F154" t="s">
+        <v>33</v>
+      </c>
+      <c r="G154" t="s">
+        <v>54</v>
+      </c>
+      <c r="H154" t="s">
+        <v>35</v>
+      </c>
+      <c r="I154">
+        <v>3</v>
+      </c>
+      <c r="J154" t="s">
+        <v>40</v>
+      </c>
+      <c r="K154">
+        <v>374</v>
+      </c>
+      <c r="L154">
+        <v>1.3315509999999999</v>
+      </c>
+      <c r="M154">
+        <v>59.333333330000002</v>
+      </c>
+      <c r="N154" t="s">
+        <v>46</v>
+      </c>
+      <c r="O154">
+        <v>0</v>
+      </c>
+      <c r="P154">
+        <v>178</v>
+      </c>
+      <c r="Q154" t="s">
+        <v>47</v>
+      </c>
+      <c r="R154">
+        <v>498</v>
+      </c>
+      <c r="S154">
+        <v>357.42971899999998</v>
+      </c>
+      <c r="T154">
+        <v>3</v>
+      </c>
+      <c r="V154">
+        <v>59.333333000000003</v>
+      </c>
+      <c r="W154">
+        <v>0.60241</v>
+      </c>
+      <c r="X154">
+        <v>4</v>
+      </c>
+      <c r="Y154">
+        <v>0.80321299999999995</v>
+      </c>
+      <c r="Z154">
+        <v>44.5</v>
+      </c>
+    </row>
+    <row r="155" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>28</v>
+      </c>
+      <c r="B155" t="s">
+        <v>29</v>
+      </c>
+      <c r="C155" t="s">
+        <v>94</v>
+      </c>
+      <c r="D155" t="s">
+        <v>31</v>
+      </c>
+      <c r="E155" t="s">
+        <v>51</v>
+      </c>
+      <c r="F155" t="s">
+        <v>33</v>
+      </c>
+      <c r="G155" t="s">
+        <v>54</v>
+      </c>
+      <c r="H155" t="s">
+        <v>35</v>
+      </c>
+      <c r="K155">
+        <v>10</v>
+      </c>
+      <c r="L155">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="N155" t="s">
+        <v>46</v>
+      </c>
+      <c r="O155">
+        <v>0</v>
+      </c>
+      <c r="P155">
+        <v>0</v>
+      </c>
+      <c r="Q155" t="s">
+        <v>47</v>
+      </c>
+      <c r="R155">
+        <v>11</v>
+      </c>
+      <c r="S155">
+        <v>0</v>
+      </c>
+      <c r="X155">
+        <v>0</v>
+      </c>
+      <c r="Y155">
+        <v>0</v>
+      </c>
+      <c r="Z155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>28</v>
+      </c>
+      <c r="B156" t="s">
+        <v>29</v>
+      </c>
+      <c r="C156" t="s">
+        <v>94</v>
+      </c>
+      <c r="D156" t="s">
+        <v>31</v>
+      </c>
+      <c r="E156" t="s">
+        <v>39</v>
+      </c>
+      <c r="F156" t="s">
+        <v>33</v>
+      </c>
+      <c r="G156" t="s">
+        <v>54</v>
+      </c>
+      <c r="H156" t="s">
+        <v>35</v>
+      </c>
+      <c r="I156">
+        <v>2</v>
+      </c>
+      <c r="J156" t="s">
+        <v>40</v>
+      </c>
+      <c r="K156">
+        <v>159</v>
+      </c>
+      <c r="L156">
+        <v>1.1635219999999999</v>
+      </c>
+      <c r="M156">
+        <v>49</v>
+      </c>
+      <c r="N156" t="s">
+        <v>46</v>
+      </c>
+      <c r="O156">
+        <v>0</v>
+      </c>
+      <c r="P156">
+        <v>98</v>
+      </c>
+      <c r="Q156" t="s">
+        <v>47</v>
+      </c>
+      <c r="R156">
+        <v>185</v>
+      </c>
+      <c r="S156">
+        <v>529.72973000000002</v>
+      </c>
+      <c r="T156">
+        <v>2</v>
+      </c>
+      <c r="V156">
+        <v>49</v>
+      </c>
+      <c r="W156">
+        <v>1.081081</v>
+      </c>
+      <c r="X156">
+        <v>9</v>
+      </c>
+      <c r="Y156">
+        <v>4.864865</v>
+      </c>
+      <c r="Z156">
+        <v>10.888889000000001</v>
+      </c>
+    </row>
+    <row r="157" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>28</v>
+      </c>
+      <c r="B157" t="s">
+        <v>29</v>
+      </c>
+      <c r="C157" t="s">
+        <v>94</v>
+      </c>
+      <c r="D157" t="s">
+        <v>31</v>
+      </c>
+      <c r="E157" t="s">
+        <v>41</v>
+      </c>
+      <c r="F157" t="s">
+        <v>33</v>
+      </c>
+      <c r="G157" t="s">
+        <v>54</v>
+      </c>
+      <c r="H157" t="s">
+        <v>35</v>
+      </c>
+      <c r="I157">
+        <v>25</v>
+      </c>
+      <c r="J157" t="s">
+        <v>40</v>
+      </c>
+      <c r="K157">
+        <v>495</v>
+      </c>
+      <c r="L157">
+        <v>1.236364</v>
+      </c>
+      <c r="M157">
+        <v>18.12</v>
+      </c>
+      <c r="N157" t="s">
+        <v>46</v>
+      </c>
+      <c r="O157">
+        <v>0</v>
+      </c>
+      <c r="P157">
+        <v>453</v>
+      </c>
+      <c r="Q157" t="s">
+        <v>47</v>
+      </c>
+      <c r="R157">
+        <v>612</v>
+      </c>
+      <c r="S157">
+        <v>740.19607800000006</v>
+      </c>
+      <c r="T157">
+        <v>25</v>
+      </c>
+      <c r="V157">
+        <v>18.12</v>
+      </c>
+      <c r="W157">
+        <v>4.0849669999999998</v>
+      </c>
+      <c r="X157">
+        <v>32</v>
+      </c>
+      <c r="Y157">
+        <v>5.228758</v>
+      </c>
+      <c r="Z157">
+        <v>14.15625</v>
+      </c>
+    </row>
+    <row r="158" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>28</v>
+      </c>
+      <c r="B158" t="s">
+        <v>29</v>
+      </c>
+      <c r="C158" t="s">
+        <v>95</v>
+      </c>
+      <c r="D158" t="s">
+        <v>31</v>
+      </c>
+      <c r="E158" t="s">
+        <v>32</v>
+      </c>
+      <c r="F158" t="s">
+        <v>33</v>
+      </c>
+      <c r="G158" t="s">
+        <v>54</v>
+      </c>
+      <c r="H158" t="s">
+        <v>35</v>
+      </c>
+      <c r="I158">
+        <v>36</v>
+      </c>
+      <c r="J158" t="s">
+        <v>40</v>
+      </c>
+      <c r="K158">
+        <v>784</v>
+      </c>
+      <c r="L158">
+        <v>1.422194</v>
+      </c>
+      <c r="M158">
+        <v>18.416666670000001</v>
+      </c>
+      <c r="N158" t="s">
+        <v>46</v>
+      </c>
+      <c r="O158">
+        <v>0</v>
+      </c>
+      <c r="P158">
+        <v>663</v>
+      </c>
+      <c r="Q158" t="s">
+        <v>62</v>
+      </c>
+      <c r="R158">
+        <v>1115</v>
+      </c>
+      <c r="S158">
+        <v>594.61883399999999</v>
+      </c>
+      <c r="T158">
+        <v>36</v>
+      </c>
+      <c r="V158">
+        <v>18.416667</v>
+      </c>
+      <c r="W158">
+        <v>3.2286999999999999</v>
+      </c>
+      <c r="X158">
+        <v>39</v>
+      </c>
+      <c r="Y158">
+        <v>3.4977580000000001</v>
+      </c>
+      <c r="Z158">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="159" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>28</v>
+      </c>
+      <c r="B159" t="s">
+        <v>29</v>
+      </c>
+      <c r="C159" t="s">
+        <v>95</v>
+      </c>
+      <c r="D159" t="s">
+        <v>31</v>
+      </c>
+      <c r="E159" t="s">
+        <v>38</v>
+      </c>
+      <c r="F159" t="s">
+        <v>33</v>
+      </c>
+      <c r="G159" t="s">
+        <v>54</v>
+      </c>
+      <c r="H159" t="s">
+        <v>35</v>
+      </c>
+      <c r="I159">
+        <v>1</v>
+      </c>
+      <c r="J159" t="s">
+        <v>40</v>
+      </c>
+      <c r="K159">
+        <v>53</v>
+      </c>
+      <c r="L159">
+        <v>1.339623</v>
+      </c>
+      <c r="M159">
+        <v>25</v>
+      </c>
+      <c r="N159" t="s">
+        <v>46</v>
+      </c>
+      <c r="O159">
+        <v>0</v>
+      </c>
+      <c r="P159">
+        <v>25</v>
+      </c>
+      <c r="Q159" t="s">
+        <v>62</v>
+      </c>
+      <c r="R159">
+        <v>71</v>
+      </c>
+      <c r="S159">
+        <v>352.11267600000002</v>
+      </c>
+      <c r="T159">
+        <v>1</v>
+      </c>
+      <c r="V159">
+        <v>25</v>
+      </c>
+      <c r="W159">
+        <v>1.4084509999999999</v>
+      </c>
+      <c r="X159">
+        <v>1</v>
+      </c>
+      <c r="Y159">
+        <v>1.4084509999999999</v>
+      </c>
+      <c r="Z159">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="160" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>28</v>
+      </c>
+      <c r="B160" t="s">
+        <v>29</v>
+      </c>
+      <c r="C160" t="s">
+        <v>95</v>
+      </c>
+      <c r="D160" t="s">
+        <v>31</v>
+      </c>
+      <c r="E160" t="s">
+        <v>39</v>
+      </c>
+      <c r="F160" t="s">
+        <v>33</v>
+      </c>
+      <c r="G160" t="s">
+        <v>54</v>
+      </c>
+      <c r="H160" t="s">
+        <v>35</v>
+      </c>
+      <c r="I160">
+        <v>65</v>
+      </c>
+      <c r="J160" t="s">
+        <v>40</v>
+      </c>
+      <c r="K160">
+        <v>1339</v>
+      </c>
+      <c r="L160">
+        <v>1.324122</v>
+      </c>
+      <c r="M160">
+        <v>16.76923077</v>
+      </c>
+      <c r="N160" t="s">
+        <v>46</v>
+      </c>
+      <c r="O160">
+        <v>0</v>
+      </c>
+      <c r="P160">
+        <v>1090</v>
+      </c>
+      <c r="Q160" t="s">
+        <v>62</v>
+      </c>
+      <c r="R160">
+        <v>1773</v>
+      </c>
+      <c r="S160">
+        <v>614.77721399999996</v>
+      </c>
+      <c r="T160">
+        <v>65</v>
+      </c>
+      <c r="V160">
+        <v>16.769231000000001</v>
+      </c>
+      <c r="W160">
+        <v>3.6661030000000001</v>
+      </c>
+      <c r="X160">
+        <v>75</v>
+      </c>
+      <c r="Y160">
+        <v>4.230118</v>
+      </c>
+      <c r="Z160">
+        <v>14.533333000000001</v>
+      </c>
+    </row>
+    <row r="161" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>28</v>
+      </c>
+      <c r="B161" t="s">
+        <v>29</v>
+      </c>
+      <c r="C161" t="s">
+        <v>95</v>
+      </c>
+      <c r="D161" t="s">
+        <v>31</v>
+      </c>
+      <c r="E161" t="s">
+        <v>41</v>
+      </c>
+      <c r="F161" t="s">
+        <v>33</v>
+      </c>
+      <c r="G161" t="s">
+        <v>54</v>
+      </c>
+      <c r="H161" t="s">
+        <v>35</v>
+      </c>
+      <c r="I161">
+        <v>61</v>
+      </c>
+      <c r="J161" t="s">
+        <v>40</v>
+      </c>
+      <c r="K161">
+        <v>892</v>
+      </c>
+      <c r="L161">
+        <v>1.298206</v>
+      </c>
+      <c r="M161">
+        <v>16.737704919999999</v>
+      </c>
+      <c r="N161" t="s">
+        <v>46</v>
+      </c>
+      <c r="O161">
+        <v>0</v>
+      </c>
+      <c r="P161">
+        <v>1021</v>
+      </c>
+      <c r="Q161" t="s">
+        <v>62</v>
+      </c>
+      <c r="R161">
+        <v>1158</v>
+      </c>
+      <c r="S161">
+        <v>881.69257300000004</v>
+      </c>
+      <c r="T161">
+        <v>61</v>
+      </c>
+      <c r="V161">
+        <v>16.737704999999998</v>
+      </c>
+      <c r="W161">
+        <v>5.267703</v>
+      </c>
+      <c r="X161">
+        <v>64</v>
+      </c>
+      <c r="Y161">
+        <v>5.52677</v>
+      </c>
+      <c r="Z161">
+        <v>15.953125</v>
+      </c>
+    </row>
+    <row r="162" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>28</v>
+      </c>
+      <c r="B162" t="s">
+        <v>29</v>
+      </c>
+      <c r="C162" t="s">
+        <v>96</v>
+      </c>
+      <c r="D162" t="s">
+        <v>31</v>
+      </c>
+      <c r="E162" t="s">
+        <v>32</v>
+      </c>
+      <c r="F162" t="s">
+        <v>33</v>
+      </c>
+      <c r="G162" t="s">
+        <v>54</v>
+      </c>
+      <c r="H162" t="s">
+        <v>35</v>
+      </c>
+      <c r="I162">
+        <v>5</v>
+      </c>
+      <c r="J162" t="s">
+        <v>40</v>
+      </c>
+      <c r="K162">
+        <v>69</v>
+      </c>
+      <c r="L162">
+        <v>1.0144930000000001</v>
+      </c>
+      <c r="M162">
+        <v>8.6</v>
+      </c>
+      <c r="N162">
+        <v>160</v>
+      </c>
+      <c r="O162" t="s">
+        <v>36</v>
+      </c>
+      <c r="P162">
+        <v>43</v>
+      </c>
+      <c r="Q162" t="s">
+        <v>49</v>
+      </c>
+      <c r="R162">
+        <v>70</v>
+      </c>
+      <c r="S162">
+        <v>614.28571399999998</v>
+      </c>
+      <c r="T162">
+        <v>5</v>
+      </c>
+      <c r="V162">
+        <v>8.6</v>
+      </c>
+      <c r="W162">
+        <v>7.1428570000000002</v>
+      </c>
+      <c r="X162">
+        <v>5</v>
+      </c>
+      <c r="Y162">
+        <v>7.1428570000000002</v>
+      </c>
+      <c r="Z162">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="163" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>28</v>
+      </c>
+      <c r="B163" t="s">
+        <v>29</v>
+      </c>
+      <c r="C163" t="s">
+        <v>96</v>
+      </c>
+      <c r="D163" t="s">
+        <v>31</v>
+      </c>
+      <c r="E163" t="s">
+        <v>38</v>
+      </c>
+      <c r="F163" t="s">
+        <v>33</v>
+      </c>
+      <c r="G163" t="s">
+        <v>54</v>
+      </c>
+      <c r="H163" t="s">
+        <v>35</v>
+      </c>
+      <c r="K163">
+        <v>3</v>
+      </c>
+      <c r="L163">
+        <v>1</v>
+      </c>
+      <c r="N163">
+        <v>160</v>
+      </c>
+      <c r="O163" t="s">
+        <v>36</v>
+      </c>
+      <c r="P163">
+        <v>0</v>
+      </c>
+      <c r="Q163" t="s">
+        <v>49</v>
+      </c>
+      <c r="R163">
+        <v>3</v>
+      </c>
+      <c r="S163">
+        <v>0</v>
+      </c>
+      <c r="X163">
+        <v>0</v>
+      </c>
+      <c r="Y163">
+        <v>0</v>
+      </c>
+      <c r="Z163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>28</v>
+      </c>
+      <c r="B164" t="s">
+        <v>29</v>
+      </c>
+      <c r="C164" t="s">
+        <v>96</v>
+      </c>
+      <c r="D164" t="s">
+        <v>31</v>
+      </c>
+      <c r="E164" t="s">
+        <v>51</v>
+      </c>
+      <c r="F164" t="s">
+        <v>33</v>
+      </c>
+      <c r="G164" t="s">
+        <v>54</v>
+      </c>
+      <c r="H164" t="s">
+        <v>35</v>
+      </c>
+      <c r="K164">
+        <v>1</v>
+      </c>
+      <c r="L164">
+        <v>1</v>
+      </c>
+      <c r="N164">
+        <v>160</v>
+      </c>
+      <c r="O164" t="s">
+        <v>36</v>
+      </c>
+      <c r="P164">
+        <v>1</v>
+      </c>
+      <c r="Q164" t="s">
+        <v>49</v>
+      </c>
+      <c r="R164">
+        <v>1</v>
+      </c>
+      <c r="S164">
+        <v>1000</v>
+      </c>
+      <c r="X164">
+        <v>0</v>
+      </c>
+      <c r="Y164">
+        <v>0</v>
+      </c>
+      <c r="Z164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>28</v>
+      </c>
+      <c r="B165" t="s">
+        <v>29</v>
+      </c>
+      <c r="C165" t="s">
+        <v>96</v>
+      </c>
+      <c r="D165" t="s">
+        <v>31</v>
+      </c>
+      <c r="E165" t="s">
+        <v>39</v>
+      </c>
+      <c r="F165" t="s">
+        <v>33</v>
+      </c>
+      <c r="G165" t="s">
+        <v>54</v>
+      </c>
+      <c r="H165" t="s">
+        <v>35</v>
+      </c>
+      <c r="K165">
+        <v>15</v>
+      </c>
+      <c r="L165">
+        <v>1</v>
+      </c>
+      <c r="N165">
+        <v>160</v>
+      </c>
+      <c r="O165" t="s">
+        <v>36</v>
+      </c>
+      <c r="P165">
+        <v>7</v>
+      </c>
+      <c r="Q165" t="s">
+        <v>49</v>
+      </c>
+      <c r="R165">
+        <v>15</v>
+      </c>
+      <c r="S165">
+        <v>466.66666700000002</v>
+      </c>
+      <c r="X165">
+        <v>0</v>
+      </c>
+      <c r="Y165">
+        <v>0</v>
+      </c>
+      <c r="Z165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>28</v>
+      </c>
+      <c r="B166" t="s">
+        <v>29</v>
+      </c>
+      <c r="C166" t="s">
+        <v>96</v>
+      </c>
+      <c r="D166" t="s">
+        <v>31</v>
+      </c>
+      <c r="E166" t="s">
+        <v>41</v>
+      </c>
+      <c r="F166" t="s">
+        <v>33</v>
+      </c>
+      <c r="G166" t="s">
+        <v>54</v>
+      </c>
+      <c r="H166" t="s">
+        <v>35</v>
+      </c>
+      <c r="I166">
+        <v>1</v>
+      </c>
+      <c r="J166" t="s">
+        <v>40</v>
+      </c>
+      <c r="K166">
+        <v>33</v>
+      </c>
+      <c r="L166">
+        <v>1.030303</v>
+      </c>
+      <c r="M166">
+        <v>35</v>
+      </c>
+      <c r="N166">
+        <v>160</v>
+      </c>
+      <c r="O166" t="s">
+        <v>36</v>
+      </c>
+      <c r="P166">
+        <v>35</v>
+      </c>
+      <c r="Q166" t="s">
+        <v>49</v>
+      </c>
+      <c r="R166">
+        <v>34</v>
+      </c>
+      <c r="S166">
+        <v>1029.4117650000001</v>
+      </c>
+      <c r="T166">
+        <v>1</v>
+      </c>
+      <c r="V166">
+        <v>35</v>
+      </c>
+      <c r="W166">
+        <v>2.941176</v>
+      </c>
+      <c r="X166">
+        <v>1</v>
+      </c>
+      <c r="Y166">
+        <v>2.941176</v>
+      </c>
+      <c r="Z166">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
